--- a/data/H131_20260619_14.xlsx
+++ b/data/H131_20260619_14.xlsx
@@ -598,7 +598,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" s="2">
-        <v>622.0</v>
+        <v>625.0</v>
       </c>
       <c r="K4" s="2">
         <v>1.0</v>
@@ -610,10 +610,10 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="2">
-        <v>622.0</v>
+        <v>625.0</v>
       </c>
       <c r="O4" s="2">
-        <v>287.0</v>
+        <v>290.0</v>
       </c>
       <c r="P4" s="2">
         <v>335.0</v>
@@ -669,7 +669,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" s="2">
-        <v>525.0</v>
+        <v>530.0</v>
       </c>
       <c r="K5" s="2">
         <v>1.0</v>
@@ -681,13 +681,13 @@
         <v>0.0</v>
       </c>
       <c r="N5" s="2">
-        <v>525.0</v>
+        <v>530.0</v>
       </c>
       <c r="O5" s="2">
-        <v>262.0</v>
+        <v>266.0</v>
       </c>
       <c r="P5" s="2">
-        <v>262.0</v>
+        <v>263.0</v>
       </c>
       <c r="Q5" s="2">
         <v>1.0</v>
@@ -811,7 +811,7 @@
         <v>515.0</v>
       </c>
       <c r="J7" s="2">
-        <v>388.0</v>
+        <v>390.0</v>
       </c>
       <c r="K7" s="2">
         <v>1.0</v>
@@ -823,13 +823,13 @@
         <v>0.0</v>
       </c>
       <c r="N7" s="2">
-        <v>388.0</v>
+        <v>390.0</v>
       </c>
       <c r="O7" s="2">
-        <v>206.0</v>
+        <v>207.0</v>
       </c>
       <c r="P7" s="2">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
       <c r="Q7" s="2">
         <v>0.0</v>
@@ -953,7 +953,7 @@
         <v>730.0</v>
       </c>
       <c r="J9" s="2">
-        <v>436.0</v>
+        <v>442.0</v>
       </c>
       <c r="K9" s="2">
         <v>1.0</v>
@@ -965,10 +965,10 @@
         <v>0.0</v>
       </c>
       <c r="N9" s="2">
-        <v>436.0</v>
+        <v>442.0</v>
       </c>
       <c r="O9" s="2">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="P9" s="2">
         <v>211.0</v>
@@ -1024,7 +1024,7 @@
         <v>311.0</v>
       </c>
       <c r="J10" s="2">
-        <v>229.0</v>
+        <v>230.0</v>
       </c>
       <c r="K10" s="2">
         <v>1.0</v>
@@ -1033,25 +1033,25 @@
         <v>1.0</v>
       </c>
       <c r="M10" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="2">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
       <c r="O10" s="2">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="P10" s="2">
         <v>126.0</v>
       </c>
       <c r="Q10" s="2">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="R10" s="2">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="S10" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T10" s="2">
         <v>0.0</v>
@@ -1063,7 +1063,7 @@
         <v>0.0</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="11">
@@ -1166,7 +1166,7 @@
         <v>815.0</v>
       </c>
       <c r="J12" s="2">
-        <v>754.0</v>
+        <v>756.0</v>
       </c>
       <c r="K12" s="2">
         <v>1.0</v>
@@ -1178,13 +1178,13 @@
         <v>0.0</v>
       </c>
       <c r="N12" s="2">
-        <v>754.0</v>
+        <v>756.0</v>
       </c>
       <c r="O12" s="2">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
       <c r="P12" s="2">
-        <v>321.0</v>
+        <v>322.0</v>
       </c>
       <c r="Q12" s="2">
         <v>0.0</v>
@@ -1308,7 +1308,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" s="2">
-        <v>928.0</v>
+        <v>1088.0</v>
       </c>
       <c r="K14" s="2">
         <v>1.0</v>
@@ -1320,13 +1320,13 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <v>928.0</v>
+        <v>1088.0</v>
       </c>
       <c r="O14" s="2">
-        <v>502.0</v>
+        <v>614.0</v>
       </c>
       <c r="P14" s="2">
-        <v>424.0</v>
+        <v>472.0</v>
       </c>
       <c r="Q14" s="2">
         <v>2.0</v>
@@ -1379,7 +1379,7 @@
         <v>791.0</v>
       </c>
       <c r="J15" s="2">
-        <v>613.0</v>
+        <v>668.0</v>
       </c>
       <c r="K15" s="2">
         <v>1.0</v>
@@ -1391,13 +1391,13 @@
         <v>0.0</v>
       </c>
       <c r="N15" s="2">
-        <v>613.0</v>
+        <v>668.0</v>
       </c>
       <c r="O15" s="2">
-        <v>307.0</v>
+        <v>351.0</v>
       </c>
       <c r="P15" s="2">
-        <v>306.0</v>
+        <v>317.0</v>
       </c>
       <c r="Q15" s="2">
         <v>0.0</v>
@@ -1521,7 +1521,7 @@
         <v>829.0</v>
       </c>
       <c r="J17" s="2">
-        <v>675.0</v>
+        <v>716.0</v>
       </c>
       <c r="K17" s="2">
         <v>1.0</v>
@@ -1533,34 +1533,34 @@
         <v>0.0</v>
       </c>
       <c r="N17" s="2">
-        <v>675.0</v>
+        <v>716.0</v>
       </c>
       <c r="O17" s="2">
-        <v>362.0</v>
+        <v>397.0</v>
       </c>
       <c r="P17" s="2">
-        <v>313.0</v>
+        <v>319.0</v>
       </c>
       <c r="Q17" s="2">
         <v>0.0</v>
       </c>
       <c r="R17" s="2">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="S17" s="2">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="T17" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U17" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="V17" s="2">
         <v>0.0</v>
       </c>
       <c r="W17" s="2">
-        <v>4.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="18">
@@ -1663,7 +1663,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" s="2">
-        <v>751.0</v>
+        <v>755.0</v>
       </c>
       <c r="K19" s="2">
         <v>1.0</v>
@@ -1675,13 +1675,13 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="2">
-        <v>751.0</v>
+        <v>755.0</v>
       </c>
       <c r="O19" s="2">
         <v>398.0</v>
       </c>
       <c r="P19" s="2">
-        <v>353.0</v>
+        <v>357.0</v>
       </c>
       <c r="Q19" s="2">
         <v>0.0</v>
@@ -1690,7 +1690,7 @@
         <v>21.0</v>
       </c>
       <c r="S19" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="T19" s="2">
         <v>8.0</v>
@@ -1702,7 +1702,7 @@
         <v>0.0</v>
       </c>
       <c r="W19" s="2">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="20">
@@ -1734,7 +1734,7 @@
         <v>1257.0</v>
       </c>
       <c r="J20" s="2">
-        <v>1048.0</v>
+        <v>1080.0</v>
       </c>
       <c r="K20" s="2">
         <v>1.0</v>
@@ -1746,13 +1746,13 @@
         <v>1.0</v>
       </c>
       <c r="N20" s="2">
-        <v>1047.0</v>
+        <v>1079.0</v>
       </c>
       <c r="O20" s="2">
-        <v>602.0</v>
+        <v>618.0</v>
       </c>
       <c r="P20" s="2">
-        <v>446.0</v>
+        <v>462.0</v>
       </c>
       <c r="Q20" s="2">
         <v>0.0</v>
@@ -1761,10 +1761,10 @@
         <v>20.0</v>
       </c>
       <c r="S20" s="2">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="T20" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="U20" s="2">
         <v>0.0</v>
@@ -1773,7 +1773,7 @@
         <v>0.0</v>
       </c>
       <c r="W20" s="2">
-        <v>47.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -1805,7 +1805,7 @@
         <v>926.0</v>
       </c>
       <c r="J21" s="2">
-        <v>700.0</v>
+        <v>714.0</v>
       </c>
       <c r="K21" s="2">
         <v>1.0</v>
@@ -1817,13 +1817,13 @@
         <v>0.0</v>
       </c>
       <c r="N21" s="2">
-        <v>700.0</v>
+        <v>714.0</v>
       </c>
       <c r="O21" s="2">
-        <v>365.0</v>
+        <v>374.0</v>
       </c>
       <c r="P21" s="2">
-        <v>335.0</v>
+        <v>340.0</v>
       </c>
       <c r="Q21" s="2">
         <v>0.0</v>
@@ -1838,13 +1838,13 @@
         <v>4.0</v>
       </c>
       <c r="U21" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="V21" s="2">
         <v>0.0</v>
       </c>
       <c r="W21" s="2">
-        <v>69.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -1876,7 +1876,7 @@
         <v>1003.0</v>
       </c>
       <c r="J22" s="2">
-        <v>851.0</v>
+        <v>870.0</v>
       </c>
       <c r="K22" s="2">
         <v>1.0</v>
@@ -1888,34 +1888,34 @@
         <v>0.0</v>
       </c>
       <c r="N22" s="2">
-        <v>851.0</v>
+        <v>870.0</v>
       </c>
       <c r="O22" s="2">
-        <v>475.0</v>
+        <v>489.0</v>
       </c>
       <c r="P22" s="2">
-        <v>376.0</v>
+        <v>381.0</v>
       </c>
       <c r="Q22" s="2">
         <v>0.0</v>
       </c>
       <c r="R22" s="2">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="S22" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="T22" s="2">
         <v>0.0</v>
       </c>
       <c r="U22" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="V22" s="2">
         <v>0.0</v>
       </c>
       <c r="W22" s="2">
-        <v>52.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -1947,7 +1947,7 @@
         <v>762.0</v>
       </c>
       <c r="J23" s="2">
-        <v>387.0</v>
+        <v>388.0</v>
       </c>
       <c r="K23" s="2">
         <v>1.0</v>
@@ -1959,10 +1959,10 @@
         <v>0.0</v>
       </c>
       <c r="N23" s="2">
-        <v>387.0</v>
+        <v>388.0</v>
       </c>
       <c r="O23" s="2">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="P23" s="2">
         <v>199.0</v>
@@ -2018,7 +2018,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>763.0</v>
+        <v>774.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2030,13 +2030,13 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>763.0</v>
+        <v>774.0</v>
       </c>
       <c r="O24" s="2">
-        <v>440.0</v>
+        <v>444.0</v>
       </c>
       <c r="P24" s="2">
-        <v>307.0</v>
+        <v>314.0</v>
       </c>
       <c r="Q24" s="2">
         <v>16.0</v>
@@ -2089,7 +2089,7 @@
         <v>372.0</v>
       </c>
       <c r="J25" s="2">
-        <v>359.0</v>
+        <v>368.0</v>
       </c>
       <c r="K25" s="2">
         <v>1.0</v>
@@ -2101,22 +2101,22 @@
         <v>0.0</v>
       </c>
       <c r="N25" s="2">
-        <v>359.0</v>
+        <v>368.0</v>
       </c>
       <c r="O25" s="2">
-        <v>256.0</v>
+        <v>263.0</v>
       </c>
       <c r="P25" s="2">
-        <v>103.0</v>
+        <v>105.0</v>
       </c>
       <c r="Q25" s="2">
         <v>0.0</v>
       </c>
       <c r="R25" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S25" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T25" s="2">
         <v>0.0</v>
@@ -2128,7 +2128,7 @@
         <v>0.0</v>
       </c>
       <c r="W25" s="2">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -2302,7 +2302,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" s="2">
-        <v>1015.0</v>
+        <v>1016.0</v>
       </c>
       <c r="K28" s="2">
         <v>1.0</v>
@@ -2314,10 +2314,10 @@
         <v>0.0</v>
       </c>
       <c r="N28" s="2">
-        <v>1015.0</v>
+        <v>1016.0</v>
       </c>
       <c r="O28" s="2">
-        <v>556.0</v>
+        <v>557.0</v>
       </c>
       <c r="P28" s="2">
         <v>457.0</v>
@@ -2373,7 +2373,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" s="2">
-        <v>494.0</v>
+        <v>582.0</v>
       </c>
       <c r="K29" s="2">
         <v>1.0</v>
@@ -2385,13 +2385,13 @@
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <v>494.0</v>
+        <v>582.0</v>
       </c>
       <c r="O29" s="2">
-        <v>108.0</v>
+        <v>145.0</v>
       </c>
       <c r="P29" s="2">
-        <v>254.0</v>
+        <v>305.0</v>
       </c>
       <c r="Q29" s="2">
         <v>132.0</v>
@@ -2444,7 +2444,7 @@
         <v>258.0</v>
       </c>
       <c r="J30" s="2">
-        <v>233.0</v>
+        <v>235.0</v>
       </c>
       <c r="K30" s="2">
         <v>1.0</v>
@@ -2456,13 +2456,13 @@
         <v>0.0</v>
       </c>
       <c r="N30" s="2">
-        <v>233.0</v>
+        <v>235.0</v>
       </c>
       <c r="O30" s="2">
         <v>133.0</v>
       </c>
       <c r="P30" s="2">
-        <v>78.0</v>
+        <v>80.0</v>
       </c>
       <c r="Q30" s="2">
         <v>22.0</v>
@@ -2515,7 +2515,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" s="2">
-        <v>859.0</v>
+        <v>928.0</v>
       </c>
       <c r="K31" s="2">
         <v>1.0</v>
@@ -2527,16 +2527,16 @@
         <v>0.0</v>
       </c>
       <c r="N31" s="2">
-        <v>859.0</v>
+        <v>928.0</v>
       </c>
       <c r="O31" s="2">
-        <v>465.0</v>
+        <v>502.0</v>
       </c>
       <c r="P31" s="2">
-        <v>387.0</v>
+        <v>417.0</v>
       </c>
       <c r="Q31" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="R31" s="2">
         <v>1.0</v>
@@ -2799,7 +2799,7 @@
         <v>554.0</v>
       </c>
       <c r="J35" s="2">
-        <v>472.0</v>
+        <v>482.0</v>
       </c>
       <c r="K35" s="2">
         <v>1.0</v>
@@ -2811,19 +2811,19 @@
         <v>0.0</v>
       </c>
       <c r="N35" s="2">
-        <v>472.0</v>
+        <v>482.0</v>
       </c>
       <c r="O35" s="2">
-        <v>253.0</v>
+        <v>259.0</v>
       </c>
       <c r="P35" s="2">
-        <v>210.0</v>
+        <v>214.0</v>
       </c>
       <c r="Q35" s="2">
         <v>9.0</v>
       </c>
       <c r="R35" s="2">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="S35" s="2">
         <v>7.0</v>
@@ -2838,7 +2838,7 @@
         <v>0.0</v>
       </c>
       <c r="W35" s="2">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
@@ -2870,7 +2870,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" s="2">
-        <v>626.0</v>
+        <v>646.0</v>
       </c>
       <c r="K36" s="2">
         <v>1.0</v>
@@ -2882,13 +2882,13 @@
         <v>0.0</v>
       </c>
       <c r="N36" s="2">
-        <v>626.0</v>
+        <v>646.0</v>
       </c>
       <c r="O36" s="2">
-        <v>293.0</v>
+        <v>303.0</v>
       </c>
       <c r="P36" s="2">
-        <v>330.0</v>
+        <v>340.0</v>
       </c>
       <c r="Q36" s="2">
         <v>3.0</v>
@@ -2941,7 +2941,7 @@
         <v>586.0</v>
       </c>
       <c r="J37" s="2">
-        <v>463.0</v>
+        <v>466.0</v>
       </c>
       <c r="K37" s="2">
         <v>1.0</v>
@@ -2953,13 +2953,13 @@
         <v>0.0</v>
       </c>
       <c r="N37" s="2">
-        <v>463.0</v>
+        <v>466.0</v>
       </c>
       <c r="O37" s="2">
-        <v>241.0</v>
+        <v>243.0</v>
       </c>
       <c r="P37" s="2">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="Q37" s="2">
         <v>4.0</v>
@@ -3083,7 +3083,7 @@
         <v>588.0</v>
       </c>
       <c r="J39" s="2">
-        <v>447.0</v>
+        <v>452.0</v>
       </c>
       <c r="K39" s="2">
         <v>1.0</v>
@@ -3095,13 +3095,13 @@
         <v>0.0</v>
       </c>
       <c r="N39" s="2">
-        <v>447.0</v>
+        <v>452.0</v>
       </c>
       <c r="O39" s="2">
-        <v>224.0</v>
+        <v>226.0</v>
       </c>
       <c r="P39" s="2">
-        <v>223.0</v>
+        <v>226.0</v>
       </c>
       <c r="Q39" s="2">
         <v>0.0</v>
@@ -3154,7 +3154,7 @@
         <v>1249.0</v>
       </c>
       <c r="J40" s="2">
-        <v>1186.0</v>
+        <v>1224.0</v>
       </c>
       <c r="K40" s="2">
         <v>1.0</v>
@@ -3166,25 +3166,25 @@
         <v>0.0</v>
       </c>
       <c r="N40" s="2">
-        <v>1186.0</v>
+        <v>1224.0</v>
       </c>
       <c r="O40" s="2">
-        <v>683.0</v>
+        <v>719.0</v>
       </c>
       <c r="P40" s="2">
-        <v>496.0</v>
+        <v>498.0</v>
       </c>
       <c r="Q40" s="2">
         <v>7.0</v>
       </c>
       <c r="R40" s="2">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="S40" s="2">
         <v>0.0</v>
       </c>
       <c r="T40" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U40" s="2">
         <v>0.0</v>
@@ -3193,7 +3193,7 @@
         <v>0.0</v>
       </c>
       <c r="W40" s="2">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -3225,7 +3225,7 @@
         <v>1244.0</v>
       </c>
       <c r="J41" s="2">
-        <v>923.0</v>
+        <v>938.0</v>
       </c>
       <c r="K41" s="2">
         <v>1.0</v>
@@ -3237,10 +3237,10 @@
         <v>0.0</v>
       </c>
       <c r="N41" s="2">
-        <v>923.0</v>
+        <v>938.0</v>
       </c>
       <c r="O41" s="2">
-        <v>437.0</v>
+        <v>452.0</v>
       </c>
       <c r="P41" s="2">
         <v>486.0</v>
@@ -3296,7 +3296,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" s="2">
-        <v>611.0</v>
+        <v>631.0</v>
       </c>
       <c r="K42" s="2">
         <v>1.0</v>
@@ -3308,19 +3308,19 @@
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <v>611.0</v>
+        <v>631.0</v>
       </c>
       <c r="O42" s="2">
-        <v>405.0</v>
+        <v>416.0</v>
       </c>
       <c r="P42" s="2">
-        <v>206.0</v>
+        <v>215.0</v>
       </c>
       <c r="Q42" s="2">
         <v>0.0</v>
       </c>
       <c r="R42" s="2">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="S42" s="2">
         <v>2.0</v>
@@ -3335,7 +3335,7 @@
         <v>0.0</v>
       </c>
       <c r="W42" s="2">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -3367,7 +3367,7 @@
         <v>1022.0</v>
       </c>
       <c r="J43" s="2">
-        <v>767.0</v>
+        <v>798.0</v>
       </c>
       <c r="K43" s="2">
         <v>1.0</v>
@@ -3379,22 +3379,22 @@
         <v>0.0</v>
       </c>
       <c r="N43" s="2">
-        <v>767.0</v>
+        <v>798.0</v>
       </c>
       <c r="O43" s="2">
-        <v>387.0</v>
+        <v>407.0</v>
       </c>
       <c r="P43" s="2">
-        <v>379.0</v>
+        <v>388.0</v>
       </c>
       <c r="Q43" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="R43" s="2">
         <v>10.0</v>
       </c>
       <c r="S43" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T43" s="2">
         <v>0.0</v>
@@ -3406,7 +3406,7 @@
         <v>0.0</v>
       </c>
       <c r="W43" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -3509,7 +3509,7 @@
         <v>1213.0</v>
       </c>
       <c r="J45" s="2">
-        <v>1059.0</v>
+        <v>1068.0</v>
       </c>
       <c r="K45" s="2">
         <v>1.0</v>
@@ -3521,25 +3521,25 @@
         <v>1.0</v>
       </c>
       <c r="N45" s="2">
-        <v>1058.0</v>
+        <v>1067.0</v>
       </c>
       <c r="O45" s="2">
-        <v>497.0</v>
+        <v>501.0</v>
       </c>
       <c r="P45" s="2">
-        <v>529.0</v>
+        <v>533.0</v>
       </c>
       <c r="Q45" s="2">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="R45" s="2">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="S45" s="2">
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
       <c r="T45" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U45" s="2">
         <v>13.0</v>
@@ -3548,7 +3548,7 @@
         <v>0.0</v>
       </c>
       <c r="W45" s="2">
-        <v>92.0</v>
+        <v>102.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
@@ -3580,7 +3580,7 @@
         <v>1429.0</v>
       </c>
       <c r="J46" s="2">
-        <v>1363.0</v>
+        <v>1373.0</v>
       </c>
       <c r="K46" s="2">
         <v>1.0</v>
@@ -3592,22 +3592,22 @@
         <v>0.0</v>
       </c>
       <c r="N46" s="2">
-        <v>1363.0</v>
+        <v>1373.0</v>
       </c>
       <c r="O46" s="2">
-        <v>706.0</v>
+        <v>707.0</v>
       </c>
       <c r="P46" s="2">
-        <v>609.0</v>
+        <v>610.0</v>
       </c>
       <c r="Q46" s="2">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
       <c r="R46" s="2">
         <v>15.0</v>
       </c>
       <c r="S46" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="T46" s="2">
         <v>18.0</v>
@@ -3619,7 +3619,7 @@
         <v>0.0</v>
       </c>
       <c r="W46" s="2">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -3651,7 +3651,7 @@
         <v>796.0</v>
       </c>
       <c r="J47" s="2">
-        <v>732.0</v>
+        <v>733.0</v>
       </c>
       <c r="K47" s="2">
         <v>1.0</v>
@@ -3663,10 +3663,10 @@
         <v>0.0</v>
       </c>
       <c r="N47" s="2">
-        <v>732.0</v>
+        <v>733.0</v>
       </c>
       <c r="O47" s="2">
-        <v>398.0</v>
+        <v>399.0</v>
       </c>
       <c r="P47" s="2">
         <v>333.0</v>
@@ -3675,7 +3675,7 @@
         <v>1.0</v>
       </c>
       <c r="R47" s="2">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="S47" s="2">
         <v>0.0</v>
@@ -3690,7 +3690,7 @@
         <v>0.0</v>
       </c>
       <c r="W47" s="2">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
@@ -3722,7 +3722,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" s="2">
-        <v>914.0</v>
+        <v>918.0</v>
       </c>
       <c r="K48" s="2">
         <v>1.0</v>
@@ -3734,13 +3734,13 @@
         <v>0.0</v>
       </c>
       <c r="N48" s="2">
-        <v>914.0</v>
+        <v>918.0</v>
       </c>
       <c r="O48" s="2">
-        <v>530.0</v>
+        <v>533.0</v>
       </c>
       <c r="P48" s="2">
-        <v>384.0</v>
+        <v>385.0</v>
       </c>
       <c r="Q48" s="2">
         <v>0.0</v>
@@ -3793,7 +3793,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" s="2">
-        <v>1028.0</v>
+        <v>1089.0</v>
       </c>
       <c r="K49" s="2">
         <v>1.0</v>
@@ -3805,13 +3805,13 @@
         <v>0.0</v>
       </c>
       <c r="N49" s="2">
-        <v>1028.0</v>
+        <v>1089.0</v>
       </c>
       <c r="O49" s="2">
-        <v>541.0</v>
+        <v>594.0</v>
       </c>
       <c r="P49" s="2">
-        <v>455.0</v>
+        <v>463.0</v>
       </c>
       <c r="Q49" s="2">
         <v>32.0</v>
@@ -3864,7 +3864,7 @@
         <v>582.0</v>
       </c>
       <c r="J50" s="2">
-        <v>518.0</v>
+        <v>525.0</v>
       </c>
       <c r="K50" s="2">
         <v>1.0</v>
@@ -3876,13 +3876,13 @@
         <v>3.0</v>
       </c>
       <c r="N50" s="2">
-        <v>515.0</v>
+        <v>522.0</v>
       </c>
       <c r="O50" s="2">
-        <v>258.0</v>
+        <v>260.0</v>
       </c>
       <c r="P50" s="2">
-        <v>232.0</v>
+        <v>237.0</v>
       </c>
       <c r="Q50" s="2">
         <v>28.0</v>
@@ -3891,7 +3891,7 @@
         <v>13.0</v>
       </c>
       <c r="S50" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T50" s="2">
         <v>0.0</v>
@@ -3903,7 +3903,7 @@
         <v>0.0</v>
       </c>
       <c r="W50" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -3935,7 +3935,7 @@
         <v>878.0</v>
       </c>
       <c r="J51" s="2">
-        <v>782.0</v>
+        <v>793.0</v>
       </c>
       <c r="K51" s="2">
         <v>1.0</v>
@@ -3947,13 +3947,13 @@
         <v>0.0</v>
       </c>
       <c r="N51" s="2">
-        <v>782.0</v>
+        <v>793.0</v>
       </c>
       <c r="O51" s="2">
-        <v>368.0</v>
+        <v>377.0</v>
       </c>
       <c r="P51" s="2">
-        <v>414.0</v>
+        <v>416.0</v>
       </c>
       <c r="Q51" s="2">
         <v>0.0</v>
@@ -4077,7 +4077,7 @@
         <v>834.0</v>
       </c>
       <c r="J53" s="2">
-        <v>811.0</v>
+        <v>820.0</v>
       </c>
       <c r="K53" s="2">
         <v>1.0</v>
@@ -4089,13 +4089,13 @@
         <v>0.0</v>
       </c>
       <c r="N53" s="2">
-        <v>811.0</v>
+        <v>820.0</v>
       </c>
       <c r="O53" s="2">
-        <v>447.0</v>
+        <v>449.0</v>
       </c>
       <c r="P53" s="2">
-        <v>358.0</v>
+        <v>365.0</v>
       </c>
       <c r="Q53" s="2">
         <v>6.0</v>
@@ -4148,7 +4148,7 @@
         <v>778.0</v>
       </c>
       <c r="J54" s="2">
-        <v>613.0</v>
+        <v>621.0</v>
       </c>
       <c r="K54" s="2">
         <v>1.0</v>
@@ -4160,19 +4160,19 @@
         <v>0.0</v>
       </c>
       <c r="N54" s="2">
-        <v>613.0</v>
+        <v>621.0</v>
       </c>
       <c r="O54" s="2">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
       <c r="P54" s="2">
-        <v>285.0</v>
+        <v>292.0</v>
       </c>
       <c r="Q54" s="2">
         <v>6.0</v>
       </c>
       <c r="R54" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S54" s="2">
         <v>104.0</v>
@@ -4187,7 +4187,7 @@
         <v>0.0</v>
       </c>
       <c r="W54" s="2">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
@@ -4219,7 +4219,7 @@
         <v>540.0</v>
       </c>
       <c r="J55" s="2">
-        <v>405.0</v>
+        <v>412.0</v>
       </c>
       <c r="K55" s="2">
         <v>1.0</v>
@@ -4231,10 +4231,10 @@
         <v>0.0</v>
       </c>
       <c r="N55" s="2">
-        <v>405.0</v>
+        <v>412.0</v>
       </c>
       <c r="O55" s="2">
-        <v>176.0</v>
+        <v>183.0</v>
       </c>
       <c r="P55" s="2">
         <v>229.0</v>
@@ -4246,7 +4246,7 @@
         <v>19.0</v>
       </c>
       <c r="S55" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="T55" s="2">
         <v>0.0</v>
@@ -4258,7 +4258,7 @@
         <v>0.0</v>
       </c>
       <c r="W55" s="2">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
@@ -4314,7 +4314,7 @@
         <v>0.0</v>
       </c>
       <c r="R56" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="S56" s="2">
         <v>0.0</v>
@@ -4329,7 +4329,7 @@
         <v>0.0</v>
       </c>
       <c r="W56" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
@@ -4361,7 +4361,7 @@
         <v>620.0</v>
       </c>
       <c r="J57" s="2">
-        <v>561.0</v>
+        <v>582.0</v>
       </c>
       <c r="K57" s="2">
         <v>1.0</v>
@@ -4373,10 +4373,10 @@
         <v>0.0</v>
       </c>
       <c r="N57" s="2">
-        <v>561.0</v>
+        <v>582.0</v>
       </c>
       <c r="O57" s="2">
-        <v>561.0</v>
+        <v>582.0</v>
       </c>
       <c r="P57" s="2">
         <v>0.0</v>
@@ -4432,7 +4432,7 @@
         <v>1059.0</v>
       </c>
       <c r="J58" s="2">
-        <v>853.0</v>
+        <v>860.0</v>
       </c>
       <c r="K58" s="2">
         <v>1.0</v>
@@ -4444,13 +4444,13 @@
         <v>0.0</v>
       </c>
       <c r="N58" s="2">
-        <v>853.0</v>
+        <v>860.0</v>
       </c>
       <c r="O58" s="2">
-        <v>451.0</v>
+        <v>457.0</v>
       </c>
       <c r="P58" s="2">
-        <v>402.0</v>
+        <v>403.0</v>
       </c>
       <c r="Q58" s="2">
         <v>0.0</v>
@@ -4503,7 +4503,7 @@
         <v>909.0</v>
       </c>
       <c r="J59" s="2">
-        <v>674.0</v>
+        <v>676.0</v>
       </c>
       <c r="K59" s="2">
         <v>1.0</v>
@@ -4515,10 +4515,10 @@
         <v>0.0</v>
       </c>
       <c r="N59" s="2">
-        <v>674.0</v>
+        <v>676.0</v>
       </c>
       <c r="O59" s="2">
-        <v>325.0</v>
+        <v>327.0</v>
       </c>
       <c r="P59" s="2">
         <v>349.0</v>
@@ -4574,7 +4574,7 @@
         <v>707.0</v>
       </c>
       <c r="J60" s="2">
-        <v>632.0</v>
+        <v>659.0</v>
       </c>
       <c r="K60" s="2">
         <v>1.0</v>
@@ -4586,13 +4586,13 @@
         <v>0.0</v>
       </c>
       <c r="N60" s="2">
-        <v>632.0</v>
+        <v>659.0</v>
       </c>
       <c r="O60" s="2">
-        <v>278.0</v>
+        <v>295.0</v>
       </c>
       <c r="P60" s="2">
-        <v>354.0</v>
+        <v>364.0</v>
       </c>
       <c r="Q60" s="2">
         <v>0.0</v>
@@ -4787,7 +4787,7 @@
         <v>1161.0</v>
       </c>
       <c r="J63" s="2">
-        <v>881.0</v>
+        <v>895.0</v>
       </c>
       <c r="K63" s="2">
         <v>1.0</v>
@@ -4799,22 +4799,22 @@
         <v>0.0</v>
       </c>
       <c r="N63" s="2">
-        <v>881.0</v>
+        <v>895.0</v>
       </c>
       <c r="O63" s="2">
-        <v>511.0</v>
+        <v>522.0</v>
       </c>
       <c r="P63" s="2">
-        <v>369.0</v>
+        <v>372.0</v>
       </c>
       <c r="Q63" s="2">
         <v>1.0</v>
       </c>
       <c r="R63" s="2">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="S63" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T63" s="2">
         <v>0.0</v>
@@ -4826,7 +4826,7 @@
         <v>0.0</v>
       </c>
       <c r="W63" s="2">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
@@ -5071,7 +5071,7 @@
         <v>1129.0</v>
       </c>
       <c r="J67" s="2">
-        <v>957.0</v>
+        <v>961.0</v>
       </c>
       <c r="K67" s="2">
         <v>1.0</v>
@@ -5083,7 +5083,7 @@
         <v>0.0</v>
       </c>
       <c r="N67" s="2">
-        <v>957.0</v>
+        <v>961.0</v>
       </c>
       <c r="O67" s="2">
         <v>451.0</v>
@@ -5092,13 +5092,13 @@
         <v>504.0</v>
       </c>
       <c r="Q67" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="R67" s="2">
         <v>58.0</v>
       </c>
       <c r="S67" s="2">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="T67" s="2">
         <v>0.0</v>
@@ -5110,7 +5110,7 @@
         <v>0.0</v>
       </c>
       <c r="W67" s="2">
-        <v>59.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
@@ -5213,7 +5213,7 @@
         <v>1124.0</v>
       </c>
       <c r="J69" s="2">
-        <v>1028.0</v>
+        <v>1049.0</v>
       </c>
       <c r="K69" s="2">
         <v>1.0</v>
@@ -5225,13 +5225,13 @@
         <v>1.0</v>
       </c>
       <c r="N69" s="2">
-        <v>1027.0</v>
+        <v>1048.0</v>
       </c>
       <c r="O69" s="2">
-        <v>546.0</v>
+        <v>565.0</v>
       </c>
       <c r="P69" s="2">
-        <v>482.0</v>
+        <v>484.0</v>
       </c>
       <c r="Q69" s="2">
         <v>0.0</v>
@@ -5284,7 +5284,7 @@
         <v>1151.0</v>
       </c>
       <c r="J70" s="2">
-        <v>1070.0</v>
+        <v>1091.0</v>
       </c>
       <c r="K70" s="2">
         <v>1.0</v>
@@ -5296,13 +5296,13 @@
         <v>0.0</v>
       </c>
       <c r="N70" s="2">
-        <v>1070.0</v>
+        <v>1091.0</v>
       </c>
       <c r="O70" s="2">
-        <v>659.0</v>
+        <v>675.0</v>
       </c>
       <c r="P70" s="2">
-        <v>401.0</v>
+        <v>406.0</v>
       </c>
       <c r="Q70" s="2">
         <v>10.0</v>
@@ -5740,7 +5740,7 @@
         <v>5.0</v>
       </c>
       <c r="T76" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="U76" s="2">
         <v>2.0</v>
@@ -5749,7 +5749,7 @@
         <v>0.0</v>
       </c>
       <c r="W76" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
@@ -5852,7 +5852,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" s="2">
-        <v>604.0</v>
+        <v>654.0</v>
       </c>
       <c r="K78" s="2">
         <v>1.0</v>
@@ -5864,13 +5864,13 @@
         <v>0.0</v>
       </c>
       <c r="N78" s="2">
-        <v>604.0</v>
+        <v>654.0</v>
       </c>
       <c r="O78" s="2">
-        <v>206.0</v>
+        <v>239.0</v>
       </c>
       <c r="P78" s="2">
-        <v>398.0</v>
+        <v>415.0</v>
       </c>
       <c r="Q78" s="2">
         <v>0.0</v>
@@ -5923,7 +5923,7 @@
         <v>786.0</v>
       </c>
       <c r="J79" s="2">
-        <v>427.0</v>
+        <v>469.0</v>
       </c>
       <c r="K79" s="2">
         <v>1.0</v>
@@ -5935,13 +5935,13 @@
         <v>0.0</v>
       </c>
       <c r="N79" s="2">
-        <v>427.0</v>
+        <v>469.0</v>
       </c>
       <c r="O79" s="2">
-        <v>208.0</v>
+        <v>236.0</v>
       </c>
       <c r="P79" s="2">
-        <v>219.0</v>
+        <v>233.0</v>
       </c>
       <c r="Q79" s="2">
         <v>0.0</v>
@@ -6278,7 +6278,7 @@
         <v>451.0</v>
       </c>
       <c r="J84" s="2">
-        <v>385.0</v>
+        <v>389.0</v>
       </c>
       <c r="K84" s="2">
         <v>1.0</v>
@@ -6290,13 +6290,13 @@
         <v>0.0</v>
       </c>
       <c r="N84" s="2">
-        <v>385.0</v>
+        <v>389.0</v>
       </c>
       <c r="O84" s="2">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="P84" s="2">
-        <v>204.0</v>
+        <v>207.0</v>
       </c>
       <c r="Q84" s="2">
         <v>0.0</v>
@@ -6305,19 +6305,19 @@
         <v>11.0</v>
       </c>
       <c r="S84" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="T84" s="2">
         <v>2.0</v>
       </c>
       <c r="U84" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="V84" s="2">
         <v>0.0</v>
       </c>
       <c r="W84" s="2">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
@@ -6349,7 +6349,7 @@
         <v>1308.0</v>
       </c>
       <c r="J85" s="2">
-        <v>1141.0</v>
+        <v>1160.0</v>
       </c>
       <c r="K85" s="2">
         <v>1.0</v>
@@ -6361,16 +6361,16 @@
         <v>0.0</v>
       </c>
       <c r="N85" s="2">
-        <v>1141.0</v>
+        <v>1160.0</v>
       </c>
       <c r="O85" s="2">
-        <v>555.0</v>
+        <v>567.0</v>
       </c>
       <c r="P85" s="2">
-        <v>581.0</v>
+        <v>587.0</v>
       </c>
       <c r="Q85" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="R85" s="2">
         <v>42.0</v>
@@ -6559,10 +6559,10 @@
         <v>883.0</v>
       </c>
       <c r="I88" s="2">
-        <v>882.0</v>
+        <v>883.0</v>
       </c>
       <c r="J88" s="2">
-        <v>656.0</v>
+        <v>661.0</v>
       </c>
       <c r="K88" s="2">
         <v>1.0</v>
@@ -6574,25 +6574,25 @@
         <v>0.0</v>
       </c>
       <c r="N88" s="2">
-        <v>656.0</v>
+        <v>661.0</v>
       </c>
       <c r="O88" s="2">
-        <v>327.0</v>
+        <v>330.0</v>
       </c>
       <c r="P88" s="2">
-        <v>329.0</v>
+        <v>331.0</v>
       </c>
       <c r="Q88" s="2">
         <v>0.0</v>
       </c>
       <c r="R88" s="2">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
       <c r="S88" s="2">
         <v>26.0</v>
       </c>
       <c r="T88" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="U88" s="2">
         <v>0.0</v>
@@ -6601,7 +6601,7 @@
         <v>1.0</v>
       </c>
       <c r="W88" s="2">
-        <v>58.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
@@ -6633,7 +6633,7 @@
         <v>814.0</v>
       </c>
       <c r="J89" s="2">
-        <v>579.0</v>
+        <v>607.0</v>
       </c>
       <c r="K89" s="2">
         <v>1.0</v>
@@ -6645,13 +6645,13 @@
         <v>0.0</v>
       </c>
       <c r="N89" s="2">
-        <v>579.0</v>
+        <v>607.0</v>
       </c>
       <c r="O89" s="2">
-        <v>306.0</v>
+        <v>325.0</v>
       </c>
       <c r="P89" s="2">
-        <v>273.0</v>
+        <v>282.0</v>
       </c>
       <c r="Q89" s="2">
         <v>0.0</v>
@@ -6704,7 +6704,7 @@
         <v>744.0</v>
       </c>
       <c r="J90" s="2">
-        <v>662.0</v>
+        <v>663.0</v>
       </c>
       <c r="K90" s="2">
         <v>1.0</v>
@@ -6716,10 +6716,10 @@
         <v>0.0</v>
       </c>
       <c r="N90" s="2">
-        <v>662.0</v>
+        <v>663.0</v>
       </c>
       <c r="O90" s="2">
-        <v>337.0</v>
+        <v>338.0</v>
       </c>
       <c r="P90" s="2">
         <v>323.0</v>
@@ -6775,7 +6775,7 @@
         <v>940.0</v>
       </c>
       <c r="J91" s="2">
-        <v>712.0</v>
+        <v>718.0</v>
       </c>
       <c r="K91" s="2">
         <v>1.0</v>
@@ -6787,34 +6787,34 @@
         <v>0.0</v>
       </c>
       <c r="N91" s="2">
-        <v>712.0</v>
+        <v>718.0</v>
       </c>
       <c r="O91" s="2">
-        <v>173.0</v>
+        <v>175.0</v>
       </c>
       <c r="P91" s="2">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="Q91" s="2">
-        <v>209.0</v>
+        <v>212.0</v>
       </c>
       <c r="R91" s="2">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="S91" s="2">
         <v>33.0</v>
       </c>
       <c r="T91" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U91" s="2">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="V91" s="2">
         <v>1.0</v>
       </c>
       <c r="W91" s="2">
-        <v>206.0</v>
+        <v>210.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
@@ -6988,7 +6988,7 @@
         <v>833.0</v>
       </c>
       <c r="J94" s="2">
-        <v>644.0</v>
+        <v>659.0</v>
       </c>
       <c r="K94" s="2">
         <v>1.0</v>
@@ -7000,13 +7000,13 @@
         <v>0.0</v>
       </c>
       <c r="N94" s="2">
-        <v>644.0</v>
+        <v>659.0</v>
       </c>
       <c r="O94" s="2">
-        <v>308.0</v>
+        <v>322.0</v>
       </c>
       <c r="P94" s="2">
-        <v>336.0</v>
+        <v>337.0</v>
       </c>
       <c r="Q94" s="2">
         <v>0.0</v>
@@ -7130,7 +7130,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" s="2">
-        <v>928.0</v>
+        <v>970.0</v>
       </c>
       <c r="K96" s="2">
         <v>1.0</v>
@@ -7142,13 +7142,13 @@
         <v>0.0</v>
       </c>
       <c r="N96" s="2">
-        <v>928.0</v>
+        <v>970.0</v>
       </c>
       <c r="O96" s="2">
-        <v>524.0</v>
+        <v>535.0</v>
       </c>
       <c r="P96" s="2">
-        <v>404.0</v>
+        <v>435.0</v>
       </c>
       <c r="Q96" s="2">
         <v>0.0</v>
@@ -7201,7 +7201,7 @@
         <v>1012.0</v>
       </c>
       <c r="J97" s="2">
-        <v>750.0</v>
+        <v>793.0</v>
       </c>
       <c r="K97" s="2">
         <v>1.0</v>
@@ -7213,13 +7213,13 @@
         <v>0.0</v>
       </c>
       <c r="N97" s="2">
-        <v>750.0</v>
+        <v>793.0</v>
       </c>
       <c r="O97" s="2">
-        <v>365.0</v>
+        <v>388.0</v>
       </c>
       <c r="P97" s="2">
-        <v>385.0</v>
+        <v>405.0</v>
       </c>
       <c r="Q97" s="2">
         <v>0.0</v>
@@ -7272,7 +7272,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>657.0</v>
+        <v>762.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7284,25 +7284,25 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>657.0</v>
+        <v>762.0</v>
       </c>
       <c r="O98" s="2">
-        <v>309.0</v>
+        <v>369.0</v>
       </c>
       <c r="P98" s="2">
-        <v>340.0</v>
+        <v>384.0</v>
       </c>
       <c r="Q98" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R98" s="2">
         <v>14.0</v>
       </c>
       <c r="S98" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="T98" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U98" s="2">
         <v>0.0</v>
@@ -7311,7 +7311,7 @@
         <v>0.0</v>
       </c>
       <c r="W98" s="2">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
@@ -7343,7 +7343,7 @@
         <v>878.0</v>
       </c>
       <c r="J99" s="2">
-        <v>756.0</v>
+        <v>759.0</v>
       </c>
       <c r="K99" s="2">
         <v>1.0</v>
@@ -7355,10 +7355,10 @@
         <v>0.0</v>
       </c>
       <c r="N99" s="2">
-        <v>756.0</v>
+        <v>759.0</v>
       </c>
       <c r="O99" s="2">
-        <v>390.0</v>
+        <v>393.0</v>
       </c>
       <c r="P99" s="2">
         <v>366.0</v>
@@ -7414,7 +7414,7 @@
         <v>1254.0</v>
       </c>
       <c r="J100" s="2">
-        <v>1090.0</v>
+        <v>1125.0</v>
       </c>
       <c r="K100" s="2">
         <v>1.0</v>
@@ -7426,10 +7426,10 @@
         <v>0.0</v>
       </c>
       <c r="N100" s="2">
-        <v>1090.0</v>
+        <v>1125.0</v>
       </c>
       <c r="O100" s="2">
-        <v>485.0</v>
+        <v>520.0</v>
       </c>
       <c r="P100" s="2">
         <v>604.0</v>
@@ -7556,7 +7556,7 @@
         <v>1159.0</v>
       </c>
       <c r="J102" s="2">
-        <v>943.0</v>
+        <v>980.0</v>
       </c>
       <c r="K102" s="2">
         <v>1.0</v>
@@ -7568,13 +7568,13 @@
         <v>0.0</v>
       </c>
       <c r="N102" s="2">
-        <v>943.0</v>
+        <v>980.0</v>
       </c>
       <c r="O102" s="2">
-        <v>479.0</v>
+        <v>505.0</v>
       </c>
       <c r="P102" s="2">
-        <v>464.0</v>
+        <v>475.0</v>
       </c>
       <c r="Q102" s="2">
         <v>0.0</v>
@@ -7583,7 +7583,7 @@
         <v>54.0</v>
       </c>
       <c r="S102" s="2">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
       <c r="T102" s="2">
         <v>0.0</v>
@@ -7595,7 +7595,7 @@
         <v>0.0</v>
       </c>
       <c r="W102" s="2">
-        <v>114.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
@@ -7627,7 +7627,7 @@
         <v>663.0</v>
       </c>
       <c r="J103" s="2">
-        <v>507.0</v>
+        <v>510.0</v>
       </c>
       <c r="K103" s="2">
         <v>1.0</v>
@@ -7639,13 +7639,13 @@
         <v>0.0</v>
       </c>
       <c r="N103" s="2">
-        <v>507.0</v>
+        <v>510.0</v>
       </c>
       <c r="O103" s="2">
-        <v>285.0</v>
+        <v>287.0</v>
       </c>
       <c r="P103" s="2">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="Q103" s="2">
         <v>0.0</v>
@@ -7654,7 +7654,7 @@
         <v>22.0</v>
       </c>
       <c r="S103" s="2">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="T103" s="2">
         <v>0.0</v>
@@ -7666,7 +7666,7 @@
         <v>0.0</v>
       </c>
       <c r="W103" s="2">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
@@ -7769,7 +7769,7 @@
         <v>1066.0</v>
       </c>
       <c r="J105" s="2">
-        <v>866.0</v>
+        <v>888.0</v>
       </c>
       <c r="K105" s="2">
         <v>1.0</v>
@@ -7781,22 +7781,22 @@
         <v>0.0</v>
       </c>
       <c r="N105" s="2">
-        <v>866.0</v>
+        <v>888.0</v>
       </c>
       <c r="O105" s="2">
-        <v>492.0</v>
+        <v>501.0</v>
       </c>
       <c r="P105" s="2">
-        <v>370.0</v>
+        <v>373.0</v>
       </c>
       <c r="Q105" s="2">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="R105" s="2">
         <v>40.0</v>
       </c>
       <c r="S105" s="2">
-        <v>113.0</v>
+        <v>117.0</v>
       </c>
       <c r="T105" s="2">
         <v>0.0</v>
@@ -7808,7 +7808,7 @@
         <v>0.0</v>
       </c>
       <c r="W105" s="2">
-        <v>153.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
@@ -7840,7 +7840,7 @@
         <v>1098.0</v>
       </c>
       <c r="J106" s="2">
-        <v>912.0</v>
+        <v>968.0</v>
       </c>
       <c r="K106" s="2">
         <v>1.0</v>
@@ -7852,16 +7852,16 @@
         <v>0.0</v>
       </c>
       <c r="N106" s="2">
-        <v>912.0</v>
+        <v>968.0</v>
       </c>
       <c r="O106" s="2">
-        <v>437.0</v>
+        <v>467.0</v>
       </c>
       <c r="P106" s="2">
-        <v>462.0</v>
+        <v>481.0</v>
       </c>
       <c r="Q106" s="2">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="R106" s="2">
         <v>32.0</v>
@@ -7870,7 +7870,7 @@
         <v>66.0</v>
       </c>
       <c r="T106" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="U106" s="2">
         <v>1.0</v>
@@ -7879,7 +7879,7 @@
         <v>0.0</v>
       </c>
       <c r="W106" s="2">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
@@ -8053,7 +8053,7 @@
         <v>821.0</v>
       </c>
       <c r="J109" s="2">
-        <v>640.0</v>
+        <v>667.0</v>
       </c>
       <c r="K109" s="2">
         <v>1.0</v>
@@ -8065,13 +8065,13 @@
         <v>0.0</v>
       </c>
       <c r="N109" s="2">
-        <v>640.0</v>
+        <v>667.0</v>
       </c>
       <c r="O109" s="2">
-        <v>342.0</v>
+        <v>362.0</v>
       </c>
       <c r="P109" s="2">
-        <v>298.0</v>
+        <v>305.0</v>
       </c>
       <c r="Q109" s="2">
         <v>0.0</v>
@@ -8124,7 +8124,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" s="2">
-        <v>501.0</v>
+        <v>511.0</v>
       </c>
       <c r="K110" s="2">
         <v>1.0</v>
@@ -8136,13 +8136,13 @@
         <v>0.0</v>
       </c>
       <c r="N110" s="2">
-        <v>501.0</v>
+        <v>511.0</v>
       </c>
       <c r="O110" s="2">
-        <v>245.0</v>
+        <v>249.0</v>
       </c>
       <c r="P110" s="2">
-        <v>256.0</v>
+        <v>262.0</v>
       </c>
       <c r="Q110" s="2">
         <v>0.0</v>
@@ -8151,7 +8151,7 @@
         <v>28.0</v>
       </c>
       <c r="S110" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="T110" s="2">
         <v>0.0</v>
@@ -8163,7 +8163,7 @@
         <v>0.0</v>
       </c>
       <c r="W110" s="2">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
@@ -8195,7 +8195,7 @@
         <v>1027.0</v>
       </c>
       <c r="J111" s="2">
-        <v>850.0</v>
+        <v>900.0</v>
       </c>
       <c r="K111" s="2">
         <v>1.0</v>
@@ -8207,10 +8207,10 @@
         <v>0.0</v>
       </c>
       <c r="N111" s="2">
-        <v>850.0</v>
+        <v>900.0</v>
       </c>
       <c r="O111" s="2">
-        <v>416.0</v>
+        <v>466.0</v>
       </c>
       <c r="P111" s="2">
         <v>429.0</v>
@@ -8222,7 +8222,7 @@
         <v>5.0</v>
       </c>
       <c r="S111" s="2">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="T111" s="2">
         <v>0.0</v>
@@ -8234,7 +8234,7 @@
         <v>0.0</v>
       </c>
       <c r="W111" s="2">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
@@ -8266,7 +8266,7 @@
         <v>709.0</v>
       </c>
       <c r="J112" s="2">
-        <v>565.0</v>
+        <v>577.0</v>
       </c>
       <c r="K112" s="2">
         <v>1.0</v>
@@ -8278,13 +8278,13 @@
         <v>0.0</v>
       </c>
       <c r="N112" s="2">
-        <v>565.0</v>
+        <v>577.0</v>
       </c>
       <c r="O112" s="2">
-        <v>291.0</v>
+        <v>293.0</v>
       </c>
       <c r="P112" s="2">
-        <v>270.0</v>
+        <v>280.0</v>
       </c>
       <c r="Q112" s="2">
         <v>4.0</v>
@@ -8296,16 +8296,16 @@
         <v>53.0</v>
       </c>
       <c r="T112" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U112" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="V112" s="2">
         <v>0.0</v>
       </c>
       <c r="W112" s="2">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
@@ -8337,7 +8337,7 @@
         <v>921.0</v>
       </c>
       <c r="J113" s="2">
-        <v>643.0</v>
+        <v>670.0</v>
       </c>
       <c r="K113" s="2">
         <v>1.0</v>
@@ -8349,10 +8349,10 @@
         <v>0.0</v>
       </c>
       <c r="N113" s="2">
-        <v>643.0</v>
+        <v>670.0</v>
       </c>
       <c r="O113" s="2">
-        <v>228.0</v>
+        <v>255.0</v>
       </c>
       <c r="P113" s="2">
         <v>415.0</v>
@@ -8408,7 +8408,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" s="2">
-        <v>552.0</v>
+        <v>556.0</v>
       </c>
       <c r="K114" s="2">
         <v>1.0</v>
@@ -8420,19 +8420,19 @@
         <v>0.0</v>
       </c>
       <c r="N114" s="2">
-        <v>552.0</v>
+        <v>556.0</v>
       </c>
       <c r="O114" s="2">
-        <v>287.0</v>
+        <v>290.0</v>
       </c>
       <c r="P114" s="2">
-        <v>264.0</v>
+        <v>265.0</v>
       </c>
       <c r="Q114" s="2">
         <v>1.0</v>
       </c>
       <c r="R114" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="S114" s="2">
         <v>0.0</v>
@@ -8447,7 +8447,7 @@
         <v>0.0</v>
       </c>
       <c r="W114" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
@@ -8621,7 +8621,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" s="2">
-        <v>653.0</v>
+        <v>656.0</v>
       </c>
       <c r="K117" s="2">
         <v>1.0</v>
@@ -8633,13 +8633,13 @@
         <v>1.0</v>
       </c>
       <c r="N117" s="2">
-        <v>652.0</v>
+        <v>655.0</v>
       </c>
       <c r="O117" s="2">
         <v>319.0</v>
       </c>
       <c r="P117" s="2">
-        <v>334.0</v>
+        <v>337.0</v>
       </c>
       <c r="Q117" s="2">
         <v>0.0</v>
@@ -8692,7 +8692,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" s="2">
-        <v>718.0</v>
+        <v>727.0</v>
       </c>
       <c r="K118" s="2">
         <v>1.0</v>
@@ -8704,13 +8704,13 @@
         <v>0.0</v>
       </c>
       <c r="N118" s="2">
-        <v>718.0</v>
+        <v>727.0</v>
       </c>
       <c r="O118" s="2">
-        <v>381.0</v>
+        <v>386.0</v>
       </c>
       <c r="P118" s="2">
-        <v>333.0</v>
+        <v>337.0</v>
       </c>
       <c r="Q118" s="2">
         <v>4.0</v>
@@ -8763,7 +8763,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" s="2">
-        <v>682.0</v>
+        <v>714.0</v>
       </c>
       <c r="K119" s="2">
         <v>1.0</v>
@@ -8775,13 +8775,13 @@
         <v>0.0</v>
       </c>
       <c r="N119" s="2">
-        <v>682.0</v>
+        <v>714.0</v>
       </c>
       <c r="O119" s="2">
-        <v>401.0</v>
+        <v>422.0</v>
       </c>
       <c r="P119" s="2">
-        <v>276.0</v>
+        <v>287.0</v>
       </c>
       <c r="Q119" s="2">
         <v>5.0</v>
@@ -8834,7 +8834,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" s="2">
-        <v>595.0</v>
+        <v>605.0</v>
       </c>
       <c r="K120" s="2">
         <v>1.0</v>
@@ -8846,13 +8846,13 @@
         <v>0.0</v>
       </c>
       <c r="N120" s="2">
-        <v>595.0</v>
+        <v>605.0</v>
       </c>
       <c r="O120" s="2">
-        <v>304.0</v>
+        <v>311.0</v>
       </c>
       <c r="P120" s="2">
-        <v>288.0</v>
+        <v>291.0</v>
       </c>
       <c r="Q120" s="2">
         <v>3.0</v>
@@ -8905,7 +8905,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" s="2">
-        <v>634.0</v>
+        <v>667.0</v>
       </c>
       <c r="K121" s="2">
         <v>1.0</v>
@@ -8917,13 +8917,13 @@
         <v>0.0</v>
       </c>
       <c r="N121" s="2">
-        <v>634.0</v>
+        <v>667.0</v>
       </c>
       <c r="O121" s="2">
-        <v>390.0</v>
+        <v>416.0</v>
       </c>
       <c r="P121" s="2">
-        <v>244.0</v>
+        <v>251.0</v>
       </c>
       <c r="Q121" s="2">
         <v>0.0</v>
@@ -8976,7 +8976,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" s="2">
-        <v>604.0</v>
+        <v>617.0</v>
       </c>
       <c r="K122" s="2">
         <v>1.0</v>
@@ -8988,13 +8988,13 @@
         <v>4.0</v>
       </c>
       <c r="N122" s="2">
-        <v>600.0</v>
+        <v>613.0</v>
       </c>
       <c r="O122" s="2">
-        <v>337.0</v>
+        <v>345.0</v>
       </c>
       <c r="P122" s="2">
-        <v>252.0</v>
+        <v>257.0</v>
       </c>
       <c r="Q122" s="2">
         <v>15.0</v>
@@ -9047,7 +9047,7 @@
         <v>623.0</v>
       </c>
       <c r="J123" s="2">
-        <v>589.0</v>
+        <v>596.0</v>
       </c>
       <c r="K123" s="2">
         <v>1.0</v>
@@ -9059,16 +9059,16 @@
         <v>0.0</v>
       </c>
       <c r="N123" s="2">
-        <v>589.0</v>
+        <v>596.0</v>
       </c>
       <c r="O123" s="2">
-        <v>305.0</v>
+        <v>309.0</v>
       </c>
       <c r="P123" s="2">
         <v>271.0</v>
       </c>
       <c r="Q123" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="R123" s="2">
         <v>13.0</v>
@@ -9260,7 +9260,7 @@
         <v>1151.0</v>
       </c>
       <c r="J126" s="2">
-        <v>850.0</v>
+        <v>852.0</v>
       </c>
       <c r="K126" s="2">
         <v>1.0</v>
@@ -9272,13 +9272,13 @@
         <v>0.0</v>
       </c>
       <c r="N126" s="2">
-        <v>850.0</v>
+        <v>852.0</v>
       </c>
       <c r="O126" s="2">
-        <v>443.0</v>
+        <v>444.0</v>
       </c>
       <c r="P126" s="2">
-        <v>389.0</v>
+        <v>390.0</v>
       </c>
       <c r="Q126" s="2">
         <v>18.0</v>
@@ -9331,7 +9331,7 @@
         <v>1150.0</v>
       </c>
       <c r="J127" s="2">
-        <v>823.0</v>
+        <v>850.0</v>
       </c>
       <c r="K127" s="2">
         <v>1.0</v>
@@ -9343,13 +9343,13 @@
         <v>0.0</v>
       </c>
       <c r="N127" s="2">
-        <v>823.0</v>
+        <v>850.0</v>
       </c>
       <c r="O127" s="2">
-        <v>527.0</v>
+        <v>542.0</v>
       </c>
       <c r="P127" s="2">
-        <v>296.0</v>
+        <v>308.0</v>
       </c>
       <c r="Q127" s="2">
         <v>0.0</v>
@@ -9358,19 +9358,19 @@
         <v>21.0</v>
       </c>
       <c r="S127" s="2">
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="T127" s="2">
         <v>2.0</v>
       </c>
       <c r="U127" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="V127" s="2">
         <v>0.0</v>
       </c>
       <c r="W127" s="2">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
@@ -9402,7 +9402,7 @@
         <v>1267.0</v>
       </c>
       <c r="J128" s="2">
-        <v>954.0</v>
+        <v>970.0</v>
       </c>
       <c r="K128" s="2">
         <v>1.0</v>
@@ -9414,19 +9414,19 @@
         <v>0.0</v>
       </c>
       <c r="N128" s="2">
-        <v>954.0</v>
+        <v>970.0</v>
       </c>
       <c r="O128" s="2">
-        <v>531.0</v>
+        <v>544.0</v>
       </c>
       <c r="P128" s="2">
-        <v>421.0</v>
+        <v>424.0</v>
       </c>
       <c r="Q128" s="2">
         <v>2.0</v>
       </c>
       <c r="R128" s="2">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="S128" s="2">
         <v>13.0</v>
@@ -9435,13 +9435,13 @@
         <v>0.0</v>
       </c>
       <c r="U128" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="V128" s="2">
         <v>0.0</v>
       </c>
       <c r="W128" s="2">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
@@ -9473,7 +9473,7 @@
         <v>1387.0</v>
       </c>
       <c r="J129" s="2">
-        <v>615.0</v>
+        <v>637.0</v>
       </c>
       <c r="K129" s="2">
         <v>1.0</v>
@@ -9485,13 +9485,13 @@
         <v>0.0</v>
       </c>
       <c r="N129" s="2">
-        <v>615.0</v>
+        <v>637.0</v>
       </c>
       <c r="O129" s="2">
-        <v>399.0</v>
+        <v>411.0</v>
       </c>
       <c r="P129" s="2">
-        <v>215.0</v>
+        <v>225.0</v>
       </c>
       <c r="Q129" s="2">
         <v>1.0</v>
@@ -9500,7 +9500,7 @@
         <v>59.0</v>
       </c>
       <c r="S129" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="T129" s="2">
         <v>0.0</v>
@@ -9512,7 +9512,7 @@
         <v>0.0</v>
       </c>
       <c r="W129" s="2">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
@@ -9544,7 +9544,7 @@
         <v>808.0</v>
       </c>
       <c r="J130" s="2">
-        <v>604.0</v>
+        <v>605.0</v>
       </c>
       <c r="K130" s="2">
         <v>1.0</v>
@@ -9556,13 +9556,13 @@
         <v>2.0</v>
       </c>
       <c r="N130" s="2">
-        <v>602.0</v>
+        <v>603.0</v>
       </c>
       <c r="O130" s="2">
         <v>394.0</v>
       </c>
       <c r="P130" s="2">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="Q130" s="2">
         <v>31.0</v>
@@ -9574,7 +9574,7 @@
         <v>10.0</v>
       </c>
       <c r="T130" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U130" s="2">
         <v>7.0</v>
@@ -9583,7 +9583,7 @@
         <v>0.0</v>
       </c>
       <c r="W130" s="2">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
@@ -9615,7 +9615,7 @@
         <v>865.0</v>
       </c>
       <c r="J131" s="2">
-        <v>580.0</v>
+        <v>582.0</v>
       </c>
       <c r="K131" s="2">
         <v>1.0</v>
@@ -9627,13 +9627,13 @@
         <v>5.0</v>
       </c>
       <c r="N131" s="2">
-        <v>575.0</v>
+        <v>577.0</v>
       </c>
       <c r="O131" s="2">
-        <v>312.0</v>
+        <v>313.0</v>
       </c>
       <c r="P131" s="2">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="Q131" s="2">
         <v>18.0</v>
@@ -9642,7 +9642,7 @@
         <v>5.0</v>
       </c>
       <c r="S131" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T131" s="2">
         <v>3.0</v>
@@ -9654,7 +9654,7 @@
         <v>0.0</v>
       </c>
       <c r="W131" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
@@ -9899,7 +9899,7 @@
         <v>1247.0</v>
       </c>
       <c r="J135" s="2">
-        <v>893.0</v>
+        <v>928.0</v>
       </c>
       <c r="K135" s="2">
         <v>1.0</v>
@@ -9911,13 +9911,13 @@
         <v>1.0</v>
       </c>
       <c r="N135" s="2">
-        <v>892.0</v>
+        <v>927.0</v>
       </c>
       <c r="O135" s="2">
-        <v>444.0</v>
+        <v>472.0</v>
       </c>
       <c r="P135" s="2">
-        <v>367.0</v>
+        <v>374.0</v>
       </c>
       <c r="Q135" s="2">
         <v>82.0</v>
@@ -9970,7 +9970,7 @@
         <v>1122.0</v>
       </c>
       <c r="J136" s="2">
-        <v>811.0</v>
+        <v>819.0</v>
       </c>
       <c r="K136" s="2">
         <v>1.0</v>
@@ -9982,13 +9982,13 @@
         <v>0.0</v>
       </c>
       <c r="N136" s="2">
-        <v>811.0</v>
+        <v>819.0</v>
       </c>
       <c r="O136" s="2">
-        <v>441.0</v>
+        <v>446.0</v>
       </c>
       <c r="P136" s="2">
-        <v>359.0</v>
+        <v>362.0</v>
       </c>
       <c r="Q136" s="2">
         <v>11.0</v>
@@ -10006,10 +10006,10 @@
         <v>4.0</v>
       </c>
       <c r="V136" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="W136" s="2">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
@@ -10041,7 +10041,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" s="2">
-        <v>607.0</v>
+        <v>627.0</v>
       </c>
       <c r="K137" s="2">
         <v>1.0</v>
@@ -10053,19 +10053,19 @@
         <v>0.0</v>
       </c>
       <c r="N137" s="2">
-        <v>607.0</v>
+        <v>627.0</v>
       </c>
       <c r="O137" s="2">
-        <v>281.0</v>
+        <v>295.0</v>
       </c>
       <c r="P137" s="2">
-        <v>312.0</v>
+        <v>318.0</v>
       </c>
       <c r="Q137" s="2">
         <v>14.0</v>
       </c>
       <c r="R137" s="2">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="S137" s="2">
         <v>15.0</v>
@@ -10080,7 +10080,7 @@
         <v>0.0</v>
       </c>
       <c r="W137" s="2">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
@@ -10112,7 +10112,7 @@
         <v>1169.0</v>
       </c>
       <c r="J138" s="2">
-        <v>723.0</v>
+        <v>766.0</v>
       </c>
       <c r="K138" s="2">
         <v>1.0</v>
@@ -10124,13 +10124,13 @@
         <v>0.0</v>
       </c>
       <c r="N138" s="2">
-        <v>723.0</v>
+        <v>766.0</v>
       </c>
       <c r="O138" s="2">
-        <v>402.0</v>
+        <v>440.0</v>
       </c>
       <c r="P138" s="2">
-        <v>297.0</v>
+        <v>302.0</v>
       </c>
       <c r="Q138" s="2">
         <v>24.0</v>
@@ -10139,7 +10139,7 @@
         <v>33.0</v>
       </c>
       <c r="S138" s="2">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="T138" s="2">
         <v>1.0</v>
@@ -10151,7 +10151,7 @@
         <v>0.0</v>
       </c>
       <c r="W138" s="2">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
@@ -10183,7 +10183,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" s="2">
-        <v>824.0</v>
+        <v>833.0</v>
       </c>
       <c r="K139" s="2">
         <v>1.0</v>
@@ -10195,22 +10195,22 @@
         <v>0.0</v>
       </c>
       <c r="N139" s="2">
-        <v>824.0</v>
+        <v>833.0</v>
       </c>
       <c r="O139" s="2">
-        <v>510.0</v>
+        <v>515.0</v>
       </c>
       <c r="P139" s="2">
-        <v>293.0</v>
+        <v>295.0</v>
       </c>
       <c r="Q139" s="2">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="R139" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="S139" s="2">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="T139" s="2">
         <v>0.0</v>
@@ -10222,7 +10222,7 @@
         <v>0.0</v>
       </c>
       <c r="W139" s="2">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
@@ -10254,7 +10254,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" s="2">
-        <v>660.0</v>
+        <v>677.0</v>
       </c>
       <c r="K140" s="2">
         <v>1.0</v>
@@ -10266,13 +10266,13 @@
         <v>0.0</v>
       </c>
       <c r="N140" s="2">
-        <v>660.0</v>
+        <v>677.0</v>
       </c>
       <c r="O140" s="2">
-        <v>336.0</v>
+        <v>347.0</v>
       </c>
       <c r="P140" s="2">
-        <v>323.0</v>
+        <v>329.0</v>
       </c>
       <c r="Q140" s="2">
         <v>1.0</v>
@@ -10281,7 +10281,7 @@
         <v>5.0</v>
       </c>
       <c r="S140" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="T140" s="2">
         <v>0.0</v>
@@ -10293,7 +10293,7 @@
         <v>0.0</v>
       </c>
       <c r="W140" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
@@ -10396,7 +10396,7 @@
         <v>1047.0</v>
       </c>
       <c r="J142" s="2">
-        <v>911.0</v>
+        <v>930.0</v>
       </c>
       <c r="K142" s="2">
         <v>1.0</v>
@@ -10408,13 +10408,13 @@
         <v>0.0</v>
       </c>
       <c r="N142" s="2">
-        <v>911.0</v>
+        <v>930.0</v>
       </c>
       <c r="O142" s="2">
-        <v>508.0</v>
+        <v>518.0</v>
       </c>
       <c r="P142" s="2">
-        <v>399.0</v>
+        <v>408.0</v>
       </c>
       <c r="Q142" s="2">
         <v>4.0</v>
@@ -10429,13 +10429,13 @@
         <v>3.0</v>
       </c>
       <c r="U142" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V142" s="2">
         <v>0.0</v>
       </c>
       <c r="W142" s="2">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
@@ -10467,7 +10467,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" s="2">
-        <v>735.0</v>
+        <v>737.0</v>
       </c>
       <c r="K143" s="2">
         <v>1.0</v>
@@ -10479,10 +10479,10 @@
         <v>1.0</v>
       </c>
       <c r="N143" s="2">
-        <v>734.0</v>
+        <v>736.0</v>
       </c>
       <c r="O143" s="2">
-        <v>442.0</v>
+        <v>444.0</v>
       </c>
       <c r="P143" s="2">
         <v>293.0</v>
@@ -10538,7 +10538,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" s="2">
-        <v>778.0</v>
+        <v>845.0</v>
       </c>
       <c r="K144" s="2">
         <v>1.0</v>
@@ -10550,13 +10550,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" s="2">
-        <v>778.0</v>
+        <v>845.0</v>
       </c>
       <c r="O144" s="2">
-        <v>412.0</v>
+        <v>465.0</v>
       </c>
       <c r="P144" s="2">
-        <v>366.0</v>
+        <v>380.0</v>
       </c>
       <c r="Q144" s="2">
         <v>0.0</v>
@@ -10751,7 +10751,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>407.0</v>
+        <v>414.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -10763,16 +10763,16 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>407.0</v>
+        <v>414.0</v>
       </c>
       <c r="O147" s="2">
-        <v>190.0</v>
+        <v>206.0</v>
       </c>
       <c r="P147" s="2">
-        <v>202.0</v>
+        <v>208.0</v>
       </c>
       <c r="Q147" s="2">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="R147" s="2">
         <v>5.0</v>
@@ -10822,7 +10822,7 @@
         <v>1269.0</v>
       </c>
       <c r="J148" s="2">
-        <v>628.0</v>
+        <v>769.0</v>
       </c>
       <c r="K148" s="2">
         <v>1.0</v>
@@ -10834,13 +10834,13 @@
         <v>0.0</v>
       </c>
       <c r="N148" s="2">
-        <v>628.0</v>
+        <v>769.0</v>
       </c>
       <c r="O148" s="2">
-        <v>245.0</v>
+        <v>302.0</v>
       </c>
       <c r="P148" s="2">
-        <v>383.0</v>
+        <v>467.0</v>
       </c>
       <c r="Q148" s="2">
         <v>0.0</v>
@@ -10893,7 +10893,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" s="2">
-        <v>574.0</v>
+        <v>609.0</v>
       </c>
       <c r="K149" s="2">
         <v>1.0</v>
@@ -10905,13 +10905,13 @@
         <v>0.0</v>
       </c>
       <c r="N149" s="2">
-        <v>574.0</v>
+        <v>609.0</v>
       </c>
       <c r="O149" s="2">
-        <v>336.0</v>
+        <v>360.0</v>
       </c>
       <c r="P149" s="2">
-        <v>234.0</v>
+        <v>245.0</v>
       </c>
       <c r="Q149" s="2">
         <v>4.0</v>
@@ -11035,7 +11035,7 @@
         <v>695.0</v>
       </c>
       <c r="J151" s="2">
-        <v>453.0</v>
+        <v>455.0</v>
       </c>
       <c r="K151" s="2">
         <v>1.0</v>
@@ -11047,10 +11047,10 @@
         <v>0.0</v>
       </c>
       <c r="N151" s="2">
-        <v>453.0</v>
+        <v>455.0</v>
       </c>
       <c r="O151" s="2">
-        <v>221.0</v>
+        <v>223.0</v>
       </c>
       <c r="P151" s="2">
         <v>232.0</v>
@@ -11248,7 +11248,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" s="2">
-        <v>574.0</v>
+        <v>599.0</v>
       </c>
       <c r="K154" s="2">
         <v>1.0</v>
@@ -11260,16 +11260,16 @@
         <v>0.0</v>
       </c>
       <c r="N154" s="2">
-        <v>574.0</v>
+        <v>599.0</v>
       </c>
       <c r="O154" s="2">
-        <v>36.0</v>
+        <v>52.0</v>
       </c>
       <c r="P154" s="2">
-        <v>313.0</v>
+        <v>319.0</v>
       </c>
       <c r="Q154" s="2">
-        <v>225.0</v>
+        <v>228.0</v>
       </c>
       <c r="R154" s="2">
         <v>0.0</v>
@@ -11461,7 +11461,7 @@
         <v>1501.0</v>
       </c>
       <c r="J157" s="2">
-        <v>800.0</v>
+        <v>805.0</v>
       </c>
       <c r="K157" s="2">
         <v>1.0</v>
@@ -11473,13 +11473,13 @@
         <v>4.0</v>
       </c>
       <c r="N157" s="2">
-        <v>796.0</v>
+        <v>801.0</v>
       </c>
       <c r="O157" s="2">
         <v>299.0</v>
       </c>
       <c r="P157" s="2">
-        <v>501.0</v>
+        <v>506.0</v>
       </c>
       <c r="Q157" s="2">
         <v>0.0</v>
@@ -11532,7 +11532,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" s="2">
-        <v>713.0</v>
+        <v>724.0</v>
       </c>
       <c r="K158" s="2">
         <v>1.0</v>
@@ -11544,19 +11544,19 @@
         <v>0.0</v>
       </c>
       <c r="N158" s="2">
-        <v>713.0</v>
+        <v>724.0</v>
       </c>
       <c r="O158" s="2">
-        <v>326.0</v>
+        <v>336.0</v>
       </c>
       <c r="P158" s="2">
-        <v>387.0</v>
+        <v>388.0</v>
       </c>
       <c r="Q158" s="2">
         <v>0.0</v>
       </c>
       <c r="R158" s="2">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
       <c r="S158" s="2">
         <v>1.0</v>
@@ -11571,7 +11571,7 @@
         <v>0.0</v>
       </c>
       <c r="W158" s="2">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
@@ -11603,7 +11603,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>804.0</v>
+        <v>812.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11615,13 +11615,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" s="2">
-        <v>803.0</v>
+        <v>811.0</v>
       </c>
       <c r="O159" s="2">
-        <v>451.0</v>
+        <v>457.0</v>
       </c>
       <c r="P159" s="2">
-        <v>353.0</v>
+        <v>355.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
@@ -11745,7 +11745,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>900.0</v>
+        <v>953.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -11757,13 +11757,13 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>900.0</v>
+        <v>953.0</v>
       </c>
       <c r="O161" s="2">
-        <v>475.0</v>
+        <v>506.0</v>
       </c>
       <c r="P161" s="2">
-        <v>417.0</v>
+        <v>439.0</v>
       </c>
       <c r="Q161" s="2">
         <v>8.0</v>
@@ -11816,7 +11816,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>807.0</v>
+        <v>831.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11828,16 +11828,16 @@
         <v>1.0</v>
       </c>
       <c r="N162" s="2">
-        <v>806.0</v>
+        <v>830.0</v>
       </c>
       <c r="O162" s="2">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
       <c r="P162" s="2">
         <v>186.0</v>
       </c>
       <c r="Q162" s="2">
-        <v>597.0</v>
+        <v>618.0</v>
       </c>
       <c r="R162" s="2">
         <v>0.0</v>
@@ -11887,7 +11887,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>716.0</v>
+        <v>726.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11899,22 +11899,22 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>716.0</v>
+        <v>726.0</v>
       </c>
       <c r="O163" s="2">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="P163" s="2">
-        <v>320.0</v>
+        <v>327.0</v>
       </c>
       <c r="Q163" s="2">
         <v>377.0</v>
       </c>
       <c r="R163" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="S163" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="T163" s="2">
         <v>0.0</v>
@@ -11926,7 +11926,7 @@
         <v>0.0</v>
       </c>
       <c r="W163" s="2">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
@@ -12100,7 +12100,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" s="2">
-        <v>629.0</v>
+        <v>637.0</v>
       </c>
       <c r="K166" s="2">
         <v>1.0</v>
@@ -12112,19 +12112,19 @@
         <v>0.0</v>
       </c>
       <c r="N166" s="2">
-        <v>629.0</v>
+        <v>637.0</v>
       </c>
       <c r="O166" s="2">
-        <v>349.0</v>
+        <v>353.0</v>
       </c>
       <c r="P166" s="2">
-        <v>280.0</v>
+        <v>284.0</v>
       </c>
       <c r="Q166" s="2">
         <v>0.0</v>
       </c>
       <c r="R166" s="2">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="S166" s="2">
         <v>3.0</v>
@@ -12139,7 +12139,7 @@
         <v>0.0</v>
       </c>
       <c r="W166" s="2">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
@@ -12313,7 +12313,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" s="2">
-        <v>429.0</v>
+        <v>439.0</v>
       </c>
       <c r="K169" s="2">
         <v>1.0</v>
@@ -12325,13 +12325,13 @@
         <v>0.0</v>
       </c>
       <c r="N169" s="2">
-        <v>429.0</v>
+        <v>439.0</v>
       </c>
       <c r="O169" s="2">
-        <v>216.0</v>
+        <v>222.0</v>
       </c>
       <c r="P169" s="2">
-        <v>205.0</v>
+        <v>209.0</v>
       </c>
       <c r="Q169" s="2">
         <v>8.0</v>
@@ -12455,7 +12455,7 @@
         <v>576.0</v>
       </c>
       <c r="J171" s="2">
-        <v>414.0</v>
+        <v>428.0</v>
       </c>
       <c r="K171" s="2">
         <v>1.0</v>
@@ -12467,13 +12467,13 @@
         <v>0.0</v>
       </c>
       <c r="N171" s="2">
-        <v>414.0</v>
+        <v>428.0</v>
       </c>
       <c r="O171" s="2">
-        <v>232.0</v>
+        <v>240.0</v>
       </c>
       <c r="P171" s="2">
-        <v>182.0</v>
+        <v>188.0</v>
       </c>
       <c r="Q171" s="2">
         <v>0.0</v>
@@ -12526,7 +12526,7 @@
         <v>1079.0</v>
       </c>
       <c r="J172" s="2">
-        <v>404.0</v>
+        <v>433.0</v>
       </c>
       <c r="K172" s="2">
         <v>1.0</v>
@@ -12538,13 +12538,13 @@
         <v>0.0</v>
       </c>
       <c r="N172" s="2">
-        <v>404.0</v>
+        <v>433.0</v>
       </c>
       <c r="O172" s="2">
-        <v>188.0</v>
+        <v>207.0</v>
       </c>
       <c r="P172" s="2">
-        <v>216.0</v>
+        <v>226.0</v>
       </c>
       <c r="Q172" s="2">
         <v>0.0</v>
@@ -12668,7 +12668,7 @@
         <v>1280.0</v>
       </c>
       <c r="J174" s="2">
-        <v>933.0</v>
+        <v>975.0</v>
       </c>
       <c r="K174" s="2">
         <v>1.0</v>
@@ -12680,10 +12680,10 @@
         <v>0.0</v>
       </c>
       <c r="N174" s="2">
-        <v>933.0</v>
+        <v>975.0</v>
       </c>
       <c r="O174" s="2">
-        <v>459.0</v>
+        <v>501.0</v>
       </c>
       <c r="P174" s="2">
         <v>474.0</v>
@@ -12739,7 +12739,7 @@
         <v>1257.0</v>
       </c>
       <c r="J175" s="2">
-        <v>948.0</v>
+        <v>992.0</v>
       </c>
       <c r="K175" s="2">
         <v>1.0</v>
@@ -12751,13 +12751,13 @@
         <v>0.0</v>
       </c>
       <c r="N175" s="2">
-        <v>948.0</v>
+        <v>992.0</v>
       </c>
       <c r="O175" s="2">
-        <v>445.0</v>
+        <v>456.0</v>
       </c>
       <c r="P175" s="2">
-        <v>503.0</v>
+        <v>536.0</v>
       </c>
       <c r="Q175" s="2">
         <v>0.0</v>
@@ -12766,7 +12766,7 @@
         <v>49.0</v>
       </c>
       <c r="S175" s="2">
-        <v>40.0</v>
+        <v>51.0</v>
       </c>
       <c r="T175" s="2">
         <v>0.0</v>
@@ -12778,7 +12778,7 @@
         <v>0.0</v>
       </c>
       <c r="W175" s="2">
-        <v>89.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
@@ -12810,7 +12810,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>523.0</v>
+        <v>530.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -12822,13 +12822,13 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>523.0</v>
+        <v>530.0</v>
       </c>
       <c r="O176" s="2">
-        <v>217.0</v>
+        <v>221.0</v>
       </c>
       <c r="P176" s="2">
-        <v>305.0</v>
+        <v>308.0</v>
       </c>
       <c r="Q176" s="2">
         <v>1.0</v>
@@ -12837,7 +12837,7 @@
         <v>61.0</v>
       </c>
       <c r="S176" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="T176" s="2">
         <v>0.0</v>
@@ -12849,7 +12849,7 @@
         <v>2.0</v>
       </c>
       <c r="W176" s="2">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
@@ -12881,7 +12881,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>489.0</v>
+        <v>504.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12893,13 +12893,13 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>489.0</v>
+        <v>504.0</v>
       </c>
       <c r="O177" s="2">
-        <v>264.0</v>
+        <v>276.0</v>
       </c>
       <c r="P177" s="2">
-        <v>225.0</v>
+        <v>228.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
@@ -13023,7 +13023,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>628.0</v>
+        <v>670.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13035,13 +13035,13 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>628.0</v>
+        <v>670.0</v>
       </c>
       <c r="O179" s="2">
-        <v>385.0</v>
+        <v>411.0</v>
       </c>
       <c r="P179" s="2">
-        <v>242.0</v>
+        <v>258.0</v>
       </c>
       <c r="Q179" s="2">
         <v>1.0</v>
@@ -13094,7 +13094,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" s="2">
-        <v>409.0</v>
+        <v>434.0</v>
       </c>
       <c r="K180" s="2">
         <v>1.0</v>
@@ -13106,13 +13106,13 @@
         <v>0.0</v>
       </c>
       <c r="N180" s="2">
-        <v>409.0</v>
+        <v>434.0</v>
       </c>
       <c r="O180" s="2">
-        <v>216.0</v>
+        <v>229.0</v>
       </c>
       <c r="P180" s="2">
-        <v>193.0</v>
+        <v>205.0</v>
       </c>
       <c r="Q180" s="2">
         <v>0.0</v>
@@ -13165,7 +13165,7 @@
         <v>855.0</v>
       </c>
       <c r="J181" s="2">
-        <v>405.0</v>
+        <v>418.0</v>
       </c>
       <c r="K181" s="2">
         <v>1.0</v>
@@ -13177,13 +13177,13 @@
         <v>0.0</v>
       </c>
       <c r="N181" s="2">
-        <v>405.0</v>
+        <v>418.0</v>
       </c>
       <c r="O181" s="2">
-        <v>214.0</v>
+        <v>217.0</v>
       </c>
       <c r="P181" s="2">
-        <v>191.0</v>
+        <v>201.0</v>
       </c>
       <c r="Q181" s="2">
         <v>0.0</v>
@@ -13378,7 +13378,7 @@
         <v>899.0</v>
       </c>
       <c r="J184" s="2">
-        <v>435.0</v>
+        <v>447.0</v>
       </c>
       <c r="K184" s="2">
         <v>1.0</v>
@@ -13390,13 +13390,13 @@
         <v>1.0</v>
       </c>
       <c r="N184" s="2">
-        <v>434.0</v>
+        <v>446.0</v>
       </c>
       <c r="O184" s="2">
-        <v>209.0</v>
+        <v>213.0</v>
       </c>
       <c r="P184" s="2">
-        <v>225.0</v>
+        <v>233.0</v>
       </c>
       <c r="Q184" s="2">
         <v>1.0</v>
@@ -13520,7 +13520,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" s="2">
-        <v>767.0</v>
+        <v>771.0</v>
       </c>
       <c r="K186" s="2">
         <v>1.0</v>
@@ -13532,16 +13532,16 @@
         <v>0.0</v>
       </c>
       <c r="N186" s="2">
-        <v>767.0</v>
+        <v>771.0</v>
       </c>
       <c r="O186" s="2">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="P186" s="2">
-        <v>328.0</v>
+        <v>330.0</v>
       </c>
       <c r="Q186" s="2">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="R186" s="2">
         <v>15.0</v>
@@ -13615,7 +13615,7 @@
         <v>0.0</v>
       </c>
       <c r="R187" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="S187" s="2">
         <v>0.0</v>
@@ -13630,7 +13630,7 @@
         <v>0.0</v>
       </c>
       <c r="W187" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="188" ht="15.75" customHeight="1">
@@ -13662,7 +13662,7 @@
         <v>1017.0</v>
       </c>
       <c r="J188" s="2">
-        <v>657.0</v>
+        <v>703.0</v>
       </c>
       <c r="K188" s="2">
         <v>1.0</v>
@@ -13674,13 +13674,13 @@
         <v>0.0</v>
       </c>
       <c r="N188" s="2">
-        <v>657.0</v>
+        <v>703.0</v>
       </c>
       <c r="O188" s="2">
-        <v>250.0</v>
+        <v>290.0</v>
       </c>
       <c r="P188" s="2">
-        <v>349.0</v>
+        <v>355.0</v>
       </c>
       <c r="Q188" s="2">
         <v>58.0</v>
@@ -13689,7 +13689,7 @@
         <v>70.0</v>
       </c>
       <c r="S188" s="2">
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="T188" s="2">
         <v>0.0</v>
@@ -13701,7 +13701,7 @@
         <v>0.0</v>
       </c>
       <c r="W188" s="2">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="189" ht="15.75" customHeight="1">
@@ -13733,7 +13733,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" s="2">
-        <v>740.0</v>
+        <v>768.0</v>
       </c>
       <c r="K189" s="2">
         <v>1.0</v>
@@ -13745,13 +13745,13 @@
         <v>0.0</v>
       </c>
       <c r="N189" s="2">
-        <v>740.0</v>
+        <v>768.0</v>
       </c>
       <c r="O189" s="2">
-        <v>216.0</v>
+        <v>243.0</v>
       </c>
       <c r="P189" s="2">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="Q189" s="2">
         <v>270.0</v>
@@ -13763,7 +13763,7 @@
         <v>0.0</v>
       </c>
       <c r="T189" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U189" s="2">
         <v>0.0</v>
@@ -13772,7 +13772,7 @@
         <v>0.0</v>
       </c>
       <c r="W189" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="190" ht="15.75" customHeight="1">
@@ -13804,7 +13804,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" s="2">
-        <v>922.0</v>
+        <v>1102.0</v>
       </c>
       <c r="K190" s="2">
         <v>1.0</v>
@@ -13816,25 +13816,25 @@
         <v>0.0</v>
       </c>
       <c r="N190" s="2">
-        <v>922.0</v>
+        <v>1102.0</v>
       </c>
       <c r="O190" s="2">
-        <v>525.0</v>
+        <v>640.0</v>
       </c>
       <c r="P190" s="2">
-        <v>376.0</v>
+        <v>435.0</v>
       </c>
       <c r="Q190" s="2">
-        <v>21.0</v>
+        <v>27.0</v>
       </c>
       <c r="R190" s="2">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="S190" s="2">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="T190" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="U190" s="2">
         <v>1.0</v>
@@ -13843,7 +13843,7 @@
         <v>0.0</v>
       </c>
       <c r="W190" s="2">
-        <v>89.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
@@ -13875,7 +13875,7 @@
         <v>1363.0</v>
       </c>
       <c r="J191" s="2">
-        <v>735.0</v>
+        <v>779.0</v>
       </c>
       <c r="K191" s="2">
         <v>1.0</v>
@@ -13887,13 +13887,13 @@
         <v>0.0</v>
       </c>
       <c r="N191" s="2">
-        <v>735.0</v>
+        <v>779.0</v>
       </c>
       <c r="O191" s="2">
-        <v>374.0</v>
+        <v>397.0</v>
       </c>
       <c r="P191" s="2">
-        <v>328.0</v>
+        <v>349.0</v>
       </c>
       <c r="Q191" s="2">
         <v>33.0</v>
@@ -13946,7 +13946,7 @@
         <v>508.0</v>
       </c>
       <c r="J192" s="2">
-        <v>378.0</v>
+        <v>402.0</v>
       </c>
       <c r="K192" s="2">
         <v>1.0</v>
@@ -13958,10 +13958,10 @@
         <v>0.0</v>
       </c>
       <c r="N192" s="2">
-        <v>378.0</v>
+        <v>402.0</v>
       </c>
       <c r="O192" s="2">
-        <v>221.0</v>
+        <v>245.0</v>
       </c>
       <c r="P192" s="2">
         <v>155.0</v>
@@ -14017,7 +14017,7 @@
         <v>1326.0</v>
       </c>
       <c r="J193" s="2">
-        <v>1003.0</v>
+        <v>1068.0</v>
       </c>
       <c r="K193" s="2">
         <v>1.0</v>
@@ -14029,16 +14029,16 @@
         <v>0.0</v>
       </c>
       <c r="N193" s="2">
-        <v>1003.0</v>
+        <v>1068.0</v>
       </c>
       <c r="O193" s="2">
-        <v>339.0</v>
+        <v>387.0</v>
       </c>
       <c r="P193" s="2">
-        <v>452.0</v>
+        <v>468.0</v>
       </c>
       <c r="Q193" s="2">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="R193" s="2">
         <v>0.0</v>
@@ -14088,7 +14088,7 @@
         <v>452.0</v>
       </c>
       <c r="J194" s="2">
-        <v>286.0</v>
+        <v>323.0</v>
       </c>
       <c r="K194" s="2">
         <v>1.0</v>
@@ -14100,13 +14100,13 @@
         <v>0.0</v>
       </c>
       <c r="N194" s="2">
-        <v>286.0</v>
+        <v>323.0</v>
       </c>
       <c r="O194" s="2">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="P194" s="2">
-        <v>177.0</v>
+        <v>194.0</v>
       </c>
       <c r="Q194" s="2">
         <v>29.0</v>
@@ -14159,7 +14159,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" s="2">
-        <v>361.0</v>
+        <v>377.0</v>
       </c>
       <c r="K195" s="2">
         <v>1.0</v>
@@ -14171,13 +14171,13 @@
         <v>0.0</v>
       </c>
       <c r="N195" s="2">
-        <v>361.0</v>
+        <v>377.0</v>
       </c>
       <c r="O195" s="2">
-        <v>84.0</v>
+        <v>96.0</v>
       </c>
       <c r="P195" s="2">
-        <v>151.0</v>
+        <v>155.0</v>
       </c>
       <c r="Q195" s="2">
         <v>126.0</v>
@@ -14230,7 +14230,7 @@
         <v>1391.0</v>
       </c>
       <c r="J196" s="2">
-        <v>1243.0</v>
+        <v>1297.0</v>
       </c>
       <c r="K196" s="2">
         <v>1.0</v>
@@ -14242,25 +14242,25 @@
         <v>0.0</v>
       </c>
       <c r="N196" s="2">
-        <v>1243.0</v>
+        <v>1297.0</v>
       </c>
       <c r="O196" s="2">
-        <v>508.0</v>
+        <v>556.0</v>
       </c>
       <c r="P196" s="2">
-        <v>537.0</v>
+        <v>543.0</v>
       </c>
       <c r="Q196" s="2">
         <v>198.0</v>
       </c>
       <c r="R196" s="2">
-        <v>22.0</v>
+        <v>38.0</v>
       </c>
       <c r="S196" s="2">
-        <v>12.0</v>
+        <v>35.0</v>
       </c>
       <c r="T196" s="2">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="U196" s="2">
         <v>0.0</v>
@@ -14269,7 +14269,7 @@
         <v>0.0</v>
       </c>
       <c r="W196" s="2">
-        <v>37.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="197" ht="15.75" customHeight="1">
@@ -14301,7 +14301,7 @@
         <v>1163.0</v>
       </c>
       <c r="J197" s="2">
-        <v>1066.0</v>
+        <v>1072.0</v>
       </c>
       <c r="K197" s="2">
         <v>1.0</v>
@@ -14313,13 +14313,13 @@
         <v>0.0</v>
       </c>
       <c r="N197" s="2">
-        <v>1066.0</v>
+        <v>1072.0</v>
       </c>
       <c r="O197" s="2">
-        <v>598.0</v>
+        <v>603.0</v>
       </c>
       <c r="P197" s="2">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="Q197" s="2">
         <v>118.0</v>
@@ -14328,10 +14328,10 @@
         <v>28.0</v>
       </c>
       <c r="S197" s="2">
-        <v>27.0</v>
+        <v>43.0</v>
       </c>
       <c r="T197" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="U197" s="2">
         <v>0.0</v>
@@ -14340,7 +14340,7 @@
         <v>0.0</v>
       </c>
       <c r="W197" s="2">
-        <v>60.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
@@ -14399,7 +14399,7 @@
         <v>35.0</v>
       </c>
       <c r="S198" s="2">
-        <v>39.0</v>
+        <v>59.0</v>
       </c>
       <c r="T198" s="2">
         <v>11.0</v>
@@ -14411,7 +14411,7 @@
         <v>0.0</v>
       </c>
       <c r="W198" s="2">
-        <v>85.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1">
@@ -14514,7 +14514,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" s="2">
-        <v>503.0</v>
+        <v>510.0</v>
       </c>
       <c r="K200" s="2">
         <v>1.0</v>
@@ -14526,13 +14526,13 @@
         <v>0.0</v>
       </c>
       <c r="N200" s="2">
-        <v>503.0</v>
+        <v>510.0</v>
       </c>
       <c r="O200" s="2">
-        <v>305.0</v>
+        <v>308.0</v>
       </c>
       <c r="P200" s="2">
-        <v>195.0</v>
+        <v>199.0</v>
       </c>
       <c r="Q200" s="2">
         <v>3.0</v>
@@ -14585,7 +14585,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" s="2">
-        <v>824.0</v>
+        <v>855.0</v>
       </c>
       <c r="K201" s="2">
         <v>1.0</v>
@@ -14597,13 +14597,13 @@
         <v>0.0</v>
       </c>
       <c r="N201" s="2">
-        <v>824.0</v>
+        <v>855.0</v>
       </c>
       <c r="O201" s="2">
-        <v>433.0</v>
+        <v>453.0</v>
       </c>
       <c r="P201" s="2">
-        <v>380.0</v>
+        <v>391.0</v>
       </c>
       <c r="Q201" s="2">
         <v>11.0</v>
@@ -14656,7 +14656,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>615.0</v>
+        <v>625.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -14668,13 +14668,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>615.0</v>
+        <v>625.0</v>
       </c>
       <c r="O202" s="2">
-        <v>357.0</v>
+        <v>366.0</v>
       </c>
       <c r="P202" s="2">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
@@ -14727,7 +14727,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" s="2">
-        <v>714.0</v>
+        <v>720.0</v>
       </c>
       <c r="K203" s="2">
         <v>1.0</v>
@@ -14739,13 +14739,13 @@
         <v>0.0</v>
       </c>
       <c r="N203" s="2">
-        <v>714.0</v>
+        <v>720.0</v>
       </c>
       <c r="O203" s="2">
-        <v>405.0</v>
+        <v>408.0</v>
       </c>
       <c r="P203" s="2">
-        <v>309.0</v>
+        <v>312.0</v>
       </c>
       <c r="Q203" s="2">
         <v>0.0</v>
@@ -14869,7 +14869,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>497.0</v>
+        <v>522.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -14881,16 +14881,16 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>497.0</v>
+        <v>522.0</v>
       </c>
       <c r="O205" s="2">
-        <v>241.0</v>
+        <v>260.0</v>
       </c>
       <c r="P205" s="2">
-        <v>222.0</v>
+        <v>227.0</v>
       </c>
       <c r="Q205" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="R205" s="2">
         <v>0.0</v>
@@ -14940,7 +14940,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" s="2">
-        <v>675.0</v>
+        <v>696.0</v>
       </c>
       <c r="K206" s="2">
         <v>1.0</v>
@@ -14952,13 +14952,13 @@
         <v>0.0</v>
       </c>
       <c r="N206" s="2">
-        <v>675.0</v>
+        <v>696.0</v>
       </c>
       <c r="O206" s="2">
-        <v>416.0</v>
+        <v>431.0</v>
       </c>
       <c r="P206" s="2">
-        <v>259.0</v>
+        <v>265.0</v>
       </c>
       <c r="Q206" s="2">
         <v>0.0</v>
@@ -15011,7 +15011,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>506.0</v>
+        <v>515.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15023,13 +15023,13 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>506.0</v>
+        <v>515.0</v>
       </c>
       <c r="O207" s="2">
-        <v>286.0</v>
+        <v>291.0</v>
       </c>
       <c r="P207" s="2">
-        <v>216.0</v>
+        <v>220.0</v>
       </c>
       <c r="Q207" s="2">
         <v>4.0</v>
@@ -15038,7 +15038,7 @@
         <v>1.0</v>
       </c>
       <c r="S207" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T207" s="2">
         <v>0.0</v>
@@ -15050,7 +15050,7 @@
         <v>0.0</v>
       </c>
       <c r="W207" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1">
@@ -15180,7 +15180,7 @@
         <v>46.0</v>
       </c>
       <c r="S209" s="2">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="T209" s="2">
         <v>2.0</v>
@@ -15192,7 +15192,7 @@
         <v>0.0</v>
       </c>
       <c r="W209" s="2">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">
@@ -15295,7 +15295,7 @@
         <v>1074.0</v>
       </c>
       <c r="J211" s="2">
-        <v>820.0</v>
+        <v>827.0</v>
       </c>
       <c r="K211" s="2">
         <v>1.0</v>
@@ -15307,13 +15307,13 @@
         <v>0.0</v>
       </c>
       <c r="N211" s="2">
-        <v>820.0</v>
+        <v>827.0</v>
       </c>
       <c r="O211" s="2">
-        <v>419.0</v>
+        <v>423.0</v>
       </c>
       <c r="P211" s="2">
-        <v>401.0</v>
+        <v>404.0</v>
       </c>
       <c r="Q211" s="2">
         <v>0.0</v>
@@ -15437,7 +15437,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" s="2">
-        <v>687.0</v>
+        <v>721.0</v>
       </c>
       <c r="K213" s="2">
         <v>1.0</v>
@@ -15449,13 +15449,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" s="2">
-        <v>687.0</v>
+        <v>721.0</v>
       </c>
       <c r="O213" s="2">
-        <v>359.0</v>
+        <v>392.0</v>
       </c>
       <c r="P213" s="2">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="Q213" s="2">
         <v>0.0</v>
@@ -15508,7 +15508,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" s="2">
-        <v>540.0</v>
+        <v>560.0</v>
       </c>
       <c r="K214" s="2">
         <v>1.0</v>
@@ -15520,13 +15520,13 @@
         <v>0.0</v>
       </c>
       <c r="N214" s="2">
-        <v>540.0</v>
+        <v>560.0</v>
       </c>
       <c r="O214" s="2">
-        <v>286.0</v>
+        <v>297.0</v>
       </c>
       <c r="P214" s="2">
-        <v>254.0</v>
+        <v>263.0</v>
       </c>
       <c r="Q214" s="2">
         <v>0.0</v>
@@ -15579,7 +15579,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" s="2">
-        <v>796.0</v>
+        <v>889.0</v>
       </c>
       <c r="K215" s="2">
         <v>1.0</v>
@@ -15591,34 +15591,34 @@
         <v>0.0</v>
       </c>
       <c r="N215" s="2">
-        <v>796.0</v>
+        <v>889.0</v>
       </c>
       <c r="O215" s="2">
-        <v>364.0</v>
+        <v>448.0</v>
       </c>
       <c r="P215" s="2">
-        <v>432.0</v>
+        <v>441.0</v>
       </c>
       <c r="Q215" s="2">
         <v>0.0</v>
       </c>
       <c r="R215" s="2">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="S215" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="T215" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="U215" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="V215" s="2">
         <v>0.0</v>
       </c>
       <c r="W215" s="2">
-        <v>28.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1">
@@ -15721,7 +15721,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" s="2">
-        <v>612.0</v>
+        <v>660.0</v>
       </c>
       <c r="K217" s="2">
         <v>1.0</v>
@@ -15733,13 +15733,13 @@
         <v>0.0</v>
       </c>
       <c r="N217" s="2">
-        <v>612.0</v>
+        <v>660.0</v>
       </c>
       <c r="O217" s="2">
-        <v>273.0</v>
+        <v>300.0</v>
       </c>
       <c r="P217" s="2">
-        <v>339.0</v>
+        <v>360.0</v>
       </c>
       <c r="Q217" s="2">
         <v>0.0</v>
@@ -15863,7 +15863,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>867.0</v>
+        <v>900.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15875,13 +15875,13 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>867.0</v>
+        <v>900.0</v>
       </c>
       <c r="O219" s="2">
-        <v>121.0</v>
+        <v>142.0</v>
       </c>
       <c r="P219" s="2">
-        <v>372.0</v>
+        <v>384.0</v>
       </c>
       <c r="Q219" s="2">
         <v>374.0</v>
@@ -15890,7 +15890,7 @@
         <v>22.0</v>
       </c>
       <c r="S219" s="2">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="T219" s="2">
         <v>3.0</v>
@@ -15902,7 +15902,7 @@
         <v>0.0</v>
       </c>
       <c r="W219" s="2">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
@@ -15934,7 +15934,7 @@
         <v>867.0</v>
       </c>
       <c r="J220" s="2">
-        <v>584.0</v>
+        <v>620.0</v>
       </c>
       <c r="K220" s="2">
         <v>1.0</v>
@@ -15946,13 +15946,13 @@
         <v>0.0</v>
       </c>
       <c r="N220" s="2">
-        <v>584.0</v>
+        <v>620.0</v>
       </c>
       <c r="O220" s="2">
-        <v>90.0</v>
+        <v>110.0</v>
       </c>
       <c r="P220" s="2">
-        <v>262.0</v>
+        <v>278.0</v>
       </c>
       <c r="Q220" s="2">
         <v>232.0</v>
@@ -16005,7 +16005,7 @@
         <v>848.0</v>
       </c>
       <c r="J221" s="2">
-        <v>605.0</v>
+        <v>607.0</v>
       </c>
       <c r="K221" s="2">
         <v>1.0</v>
@@ -16017,10 +16017,10 @@
         <v>1.0</v>
       </c>
       <c r="N221" s="2">
-        <v>604.0</v>
+        <v>606.0</v>
       </c>
       <c r="O221" s="2">
-        <v>115.0</v>
+        <v>117.0</v>
       </c>
       <c r="P221" s="2">
         <v>244.0</v>
@@ -16029,13 +16029,13 @@
         <v>246.0</v>
       </c>
       <c r="R221" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S221" s="2">
         <v>0.0</v>
       </c>
       <c r="T221" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U221" s="2">
         <v>0.0</v>
@@ -16044,7 +16044,7 @@
         <v>0.0</v>
       </c>
       <c r="W221" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1">
@@ -16076,7 +16076,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" s="2">
-        <v>652.0</v>
+        <v>655.0</v>
       </c>
       <c r="K222" s="2">
         <v>1.0</v>
@@ -16088,10 +16088,10 @@
         <v>0.0</v>
       </c>
       <c r="N222" s="2">
-        <v>652.0</v>
+        <v>655.0</v>
       </c>
       <c r="O222" s="2">
-        <v>140.0</v>
+        <v>143.0</v>
       </c>
       <c r="P222" s="2">
         <v>276.0</v>
@@ -16147,7 +16147,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" s="2">
-        <v>769.0</v>
+        <v>798.0</v>
       </c>
       <c r="K223" s="2">
         <v>1.0</v>
@@ -16159,7 +16159,7 @@
         <v>0.0</v>
       </c>
       <c r="N223" s="2">
-        <v>769.0</v>
+        <v>798.0</v>
       </c>
       <c r="O223" s="2">
         <v>94.0</v>
@@ -16168,7 +16168,7 @@
         <v>263.0</v>
       </c>
       <c r="Q223" s="2">
-        <v>412.0</v>
+        <v>441.0</v>
       </c>
       <c r="R223" s="2">
         <v>54.0</v>
@@ -16242,7 +16242,7 @@
         <v>437.0</v>
       </c>
       <c r="R224" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S224" s="2">
         <v>0.0</v>
@@ -16257,7 +16257,7 @@
         <v>0.0</v>
       </c>
       <c r="W224" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="225" ht="15.75" customHeight="1">
@@ -16526,7 +16526,7 @@
         <v>323.0</v>
       </c>
       <c r="R228" s="2">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="S228" s="2">
         <v>0.0</v>
@@ -16541,7 +16541,7 @@
         <v>0.0</v>
       </c>
       <c r="W228" s="2">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
@@ -16573,7 +16573,7 @@
         <v>832.0</v>
       </c>
       <c r="J229" s="2">
-        <v>781.0</v>
+        <v>782.0</v>
       </c>
       <c r="K229" s="2">
         <v>1.0</v>
@@ -16585,10 +16585,10 @@
         <v>0.0</v>
       </c>
       <c r="N229" s="2">
-        <v>781.0</v>
+        <v>782.0</v>
       </c>
       <c r="O229" s="2">
-        <v>445.0</v>
+        <v>446.0</v>
       </c>
       <c r="P229" s="2">
         <v>336.0</v>
@@ -16600,19 +16600,19 @@
         <v>19.0</v>
       </c>
       <c r="S229" s="2">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="T229" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U229" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V229" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W229" s="2">
-        <v>19.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="230" ht="15.75" customHeight="1">
@@ -16644,7 +16644,7 @@
         <v>934.0</v>
       </c>
       <c r="J230" s="2">
-        <v>560.0</v>
+        <v>584.0</v>
       </c>
       <c r="K230" s="2">
         <v>1.0</v>
@@ -16656,13 +16656,13 @@
         <v>0.0</v>
       </c>
       <c r="N230" s="2">
-        <v>560.0</v>
+        <v>584.0</v>
       </c>
       <c r="O230" s="2">
-        <v>112.0</v>
+        <v>123.0</v>
       </c>
       <c r="P230" s="2">
-        <v>256.0</v>
+        <v>269.0</v>
       </c>
       <c r="Q230" s="2">
         <v>192.0</v>
@@ -16715,7 +16715,7 @@
         <v>1070.0</v>
       </c>
       <c r="J231" s="2">
-        <v>767.0</v>
+        <v>784.0</v>
       </c>
       <c r="K231" s="2">
         <v>1.0</v>
@@ -16727,13 +16727,13 @@
         <v>0.0</v>
       </c>
       <c r="N231" s="2">
-        <v>767.0</v>
+        <v>784.0</v>
       </c>
       <c r="O231" s="2">
-        <v>401.0</v>
+        <v>411.0</v>
       </c>
       <c r="P231" s="2">
-        <v>345.0</v>
+        <v>352.0</v>
       </c>
       <c r="Q231" s="2">
         <v>21.0</v>
@@ -16742,10 +16742,10 @@
         <v>12.0</v>
       </c>
       <c r="S231" s="2">
-        <v>70.0</v>
+        <v>73.0</v>
       </c>
       <c r="T231" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U231" s="2">
         <v>3.0</v>
@@ -16754,7 +16754,7 @@
         <v>0.0</v>
       </c>
       <c r="W231" s="2">
-        <v>86.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
@@ -16786,7 +16786,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" s="2">
-        <v>698.0</v>
+        <v>715.0</v>
       </c>
       <c r="K232" s="2">
         <v>1.0</v>
@@ -16798,16 +16798,16 @@
         <v>0.0</v>
       </c>
       <c r="N232" s="2">
-        <v>698.0</v>
+        <v>715.0</v>
       </c>
       <c r="O232" s="2">
-        <v>20.0</v>
+        <v>27.0</v>
       </c>
       <c r="P232" s="2">
-        <v>129.0</v>
+        <v>137.0</v>
       </c>
       <c r="Q232" s="2">
-        <v>549.0</v>
+        <v>551.0</v>
       </c>
       <c r="R232" s="2">
         <v>1.0</v>
